--- a/tests/reference_data/test_scenario_stock_lt_overrides.xlsx
+++ b/tests/reference_data/test_scenario_stock_lt_overrides.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\PythonProjects\aiphoria\tests\reference_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84D94F3C-2D48-4D2E-87F5-E0E41E63178F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B6C6F6-3283-40C7-AD05-DAA25C06FB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
+    <workbookView xWindow="-22890" yWindow="3600" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="11" r:id="rId1"/>
@@ -23,8 +23,8 @@
     <sheet name="Data validation parameters" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flows!$A$3:$P$13</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Processes!$D$3:$R$3</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flows!$A$3:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Processes!$D$3:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Settings!$B$6:$E$6</definedName>
     <definedName name="Boolean">'Data validation parameters'!$C$6:$C$7</definedName>
   </definedNames>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="552" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="244">
   <si>
     <t>Years</t>
   </si>
@@ -81,15 +81,6 @@
     <t>%</t>
   </si>
   <si>
-    <t xml:space="preserve"> kg/m3</t>
-  </si>
-  <si>
-    <t>Density</t>
-  </si>
-  <si>
-    <t>Modelling status</t>
-  </si>
-  <si>
     <t>Comment</t>
   </si>
   <si>
@@ -166,9 +157,6 @@
   </si>
   <si>
     <t>Normal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Random input values </t>
   </si>
   <si>
     <t>Sawmilling:FI</t>
@@ -563,21 +551,9 @@
     <t>Transformation stage</t>
   </si>
   <si>
-    <t>Lifetime source</t>
-  </si>
-  <si>
     <t>Distribution parameters</t>
   </si>
   <si>
-    <t>Wood content</t>
-  </si>
-  <si>
-    <t>Wood content source</t>
-  </si>
-  <si>
-    <t>Density source</t>
-  </si>
-  <si>
     <t>ignore_columns_scenarios</t>
   </si>
   <si>
@@ -606,12 +582,6 @@
   </si>
   <si>
     <t>Target ID</t>
-  </si>
-  <si>
-    <t>Data source</t>
-  </si>
-  <si>
-    <t>Data source comment</t>
   </si>
   <si>
     <t>baseline_value_name</t>
@@ -864,7 +834,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -893,12 +863,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF4C4845"/>
-      <name val="Open Sans"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
@@ -1002,29 +966,22 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment wrapText="1"/>
@@ -1036,14 +993,14 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="49" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
@@ -1518,585 +1475,585 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="21" x14ac:dyDescent="0.35">
-      <c r="B2" s="19" t="s">
-        <v>62</v>
+      <c r="B2" s="16" t="s">
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="21" t="s">
-        <v>81</v>
+      <c r="B3" s="18" t="s">
+        <v>77</v>
       </c>
     </row>
     <row r="4" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B4" t="s">
-        <v>80</v>
-      </c>
-      <c r="C4" s="21"/>
-      <c r="D4" s="21"/>
-      <c r="E4" s="21"/>
+        <v>76</v>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="18"/>
+      <c r="E4" s="18"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="9" t="s">
-        <v>63</v>
-      </c>
-      <c r="C6" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="D6" s="9" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" s="9" t="s">
+      <c r="B6" s="6" t="s">
+        <v>59</v>
+      </c>
+      <c r="C6" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>78</v>
+      </c>
+      <c r="E6" s="6" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>64</v>
-      </c>
-      <c r="C7" s="23" t="s">
+        <v>60</v>
+      </c>
+      <c r="C7" s="20" t="s">
         <v>1</v>
       </c>
-      <c r="D7" s="23" t="s">
-        <v>92</v>
+      <c r="D7" s="20" t="s">
+        <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>238</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="C8" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D8" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E8" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>65</v>
-      </c>
-      <c r="C9" s="22">
+        <v>61</v>
+      </c>
+      <c r="C9" s="19">
         <v>2</v>
       </c>
-      <c r="D9" s="22" t="s">
-        <v>90</v>
+      <c r="D9" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="E9" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>66</v>
-      </c>
-      <c r="C10" s="23" t="s">
+        <v>62</v>
+      </c>
+      <c r="C10" s="20" t="s">
         <v>2</v>
       </c>
-      <c r="D10" s="23" t="s">
-        <v>91</v>
+      <c r="D10" s="20" t="s">
+        <v>87</v>
       </c>
       <c r="E10" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="C11" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D11" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E11" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>67</v>
-      </c>
-      <c r="C12" s="22">
+        <v>63</v>
+      </c>
+      <c r="C12" s="19">
         <v>2</v>
       </c>
-      <c r="D12" s="22" t="s">
-        <v>90</v>
+      <c r="D12" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="E12" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>69</v>
-      </c>
-      <c r="C13" s="22">
+        <v>65</v>
+      </c>
+      <c r="C13" s="19">
         <v>2021</v>
       </c>
-      <c r="D13" s="22" t="s">
-        <v>90</v>
+      <c r="D13" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>71</v>
-      </c>
-      <c r="C14" s="22">
+        <v>67</v>
+      </c>
+      <c r="C14" s="19">
         <v>2030</v>
       </c>
-      <c r="D14" s="22" t="s">
-        <v>90</v>
+      <c r="D14" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>72</v>
-      </c>
-      <c r="C15" s="24" t="b">
+        <v>68</v>
+      </c>
+      <c r="C15" s="21" t="b">
         <v>0</v>
       </c>
       <c r="D15" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>75</v>
-      </c>
-      <c r="C16" s="24" t="b">
+        <v>71</v>
+      </c>
+      <c r="C16" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D16" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
-        <v>83</v>
-      </c>
-      <c r="C17" s="14">
+        <v>79</v>
+      </c>
+      <c r="C17" s="11">
         <v>0.1</v>
       </c>
-      <c r="D17" s="22" t="s">
-        <v>93</v>
+      <c r="D17" s="19" t="s">
+        <v>89</v>
       </c>
       <c r="E17" t="s">
-        <v>84</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B18" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C18" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
       <c r="D18" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E18" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B19" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
       <c r="C19" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
       <c r="D19" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B20" t="s">
-        <v>77</v>
-      </c>
-      <c r="C20" s="20">
+        <v>73</v>
+      </c>
+      <c r="C20" s="17">
         <v>-3.6666666666666701</v>
       </c>
-      <c r="D20" s="20" t="s">
-        <v>93</v>
+      <c r="D20" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="E20" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B21" t="s">
-        <v>87</v>
-      </c>
-      <c r="C21" s="24" t="b">
+        <v>83</v>
+      </c>
+      <c r="C21" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D21" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E21" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B22" t="s">
-        <v>86</v>
-      </c>
-      <c r="C22" s="24" t="b">
+        <v>82</v>
+      </c>
+      <c r="C22" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D22" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E22" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B23" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="C23" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="D23" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E23" t="s">
-        <v>115</v>
+        <v>111</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B24" t="s">
-        <v>185</v>
-      </c>
-      <c r="C24" s="24" t="b">
+        <v>175</v>
+      </c>
+      <c r="C24" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D24" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E24" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B25" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="C25" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="D25" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E25" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B26" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="C26" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="D26" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E26" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B27" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="D27" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E27" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
-      </c>
-      <c r="C28" s="24" t="b">
+        <v>98</v>
+      </c>
+      <c r="C28" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D28" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E28" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B29" t="s">
-        <v>104</v>
-      </c>
-      <c r="C29" s="24" t="b">
+        <v>100</v>
+      </c>
+      <c r="C29" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D29" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B30" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="C30" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D30" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E30" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B31" t="s">
-        <v>143</v>
-      </c>
-      <c r="C31" s="22" t="s">
-        <v>144</v>
-      </c>
-      <c r="D31" s="22" t="s">
-        <v>91</v>
+        <v>139</v>
+      </c>
+      <c r="C31" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D31" s="19" t="s">
+        <v>87</v>
       </c>
       <c r="E31" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B32" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="D32" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E32" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
     </row>
     <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B33" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D33" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E33" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B34" t="s">
-        <v>239</v>
+        <v>229</v>
       </c>
       <c r="D34" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E34" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C35" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D35" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E35" t="s">
-        <v>234</v>
+        <v>224</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B36" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="C36" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="D36" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E36" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B37" t="s">
-        <v>213</v>
-      </c>
-      <c r="C37" s="24" t="b">
+        <v>203</v>
+      </c>
+      <c r="C37" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D37" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E37" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B38" t="s">
-        <v>225</v>
-      </c>
-      <c r="C38" s="24" t="b">
+        <v>215</v>
+      </c>
+      <c r="C38" s="21" t="b">
         <v>1</v>
       </c>
       <c r="D38" t="s">
-        <v>89</v>
+        <v>85</v>
       </c>
       <c r="E38" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B39" t="s">
-        <v>227</v>
+        <v>217</v>
       </c>
       <c r="C39" t="s">
-        <v>228</v>
+        <v>218</v>
       </c>
       <c r="D39" t="s">
-        <v>91</v>
+        <v>87</v>
       </c>
       <c r="E39" t="s">
-        <v>233</v>
+        <v>223</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B40" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="C40" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
       <c r="D40" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="E40" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="B41" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="C41">
         <v>2</v>
       </c>
       <c r="D41" t="s">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="E41" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
     </row>
   </sheetData>
@@ -2171,7 +2128,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32C0D592-75C1-4AD1-84F0-2AAE25CA0097}">
-  <dimension ref="A1:R18"/>
+  <dimension ref="A1:L18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.7109375" customWidth="1"/>
@@ -2180,20 +2137,14 @@
     <col min="4" max="4" width="23.28515625" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="16.5703125" customWidth="1"/>
     <col min="6" max="6" width="12.5703125" customWidth="1"/>
-    <col min="7" max="7" width="17" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="25" customWidth="1"/>
-    <col min="10" max="10" width="17.42578125" customWidth="1"/>
-    <col min="11" max="11" width="24.5703125" customWidth="1"/>
-    <col min="12" max="12" width="9.85546875" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" customWidth="1"/>
-    <col min="14" max="14" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="12.85546875" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="19.85546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="25" customWidth="1"/>
+    <col min="9" max="9" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.85546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="19.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:18" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A1" s="1"/>
       <c r="B1" s="2" t="s">
         <v>5</v>
@@ -2210,42 +2161,26 @@
       <c r="F1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="G1" s="2"/>
+      <c r="G1" s="2" t="s">
+        <v>5</v>
+      </c>
       <c r="H1" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="I1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>61</v>
-      </c>
       <c r="J1" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="K1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="L1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="L1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="O1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="Q1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="R1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="1"/>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
@@ -2255,389 +2190,359 @@
         <v>0</v>
       </c>
       <c r="G2" s="2"/>
-      <c r="H2" s="2"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="K2" s="2"/>
-      <c r="L2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2"/>
-      <c r="P2" s="2"/>
-      <c r="Q2" s="1"/>
-      <c r="R2" s="1"/>
-    </row>
-    <row r="3" spans="1:18" s="17" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>183</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="C3" s="16" t="s">
-        <v>154</v>
-      </c>
-      <c r="D3" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="E3" s="16" t="s">
-        <v>155</v>
-      </c>
-      <c r="F3" s="16" t="s">
-        <v>60</v>
-      </c>
-      <c r="G3" s="16" t="s">
-        <v>156</v>
-      </c>
-      <c r="H3" s="16" t="s">
-        <v>85</v>
-      </c>
-      <c r="I3" s="16" t="s">
-        <v>157</v>
-      </c>
-      <c r="J3" s="16" t="s">
-        <v>158</v>
-      </c>
-      <c r="K3" s="16" t="s">
-        <v>159</v>
-      </c>
-      <c r="L3" s="16" t="s">
-        <v>11</v>
-      </c>
-      <c r="M3" s="16" t="s">
-        <v>160</v>
-      </c>
-      <c r="N3" s="16" t="s">
-        <v>12</v>
-      </c>
-      <c r="O3" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="P3" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="Q3" s="16" t="s">
+      <c r="H2" s="4"/>
+      <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="1"/>
+      <c r="L2" s="1"/>
+    </row>
+    <row r="3" spans="1:12" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>173</v>
+      </c>
+      <c r="B3" s="13" t="s">
+        <v>55</v>
+      </c>
+      <c r="C3" s="13" t="s">
+        <v>150</v>
+      </c>
+      <c r="D3" s="13" t="s">
+        <v>38</v>
+      </c>
+      <c r="E3" s="13" t="s">
+        <v>151</v>
+      </c>
+      <c r="F3" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="G3" s="13" t="s">
+        <v>81</v>
+      </c>
+      <c r="H3" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="I3" s="13" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="K3" s="13" t="s">
+        <v>18</v>
+      </c>
+      <c r="L3" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="R3" s="16" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="4" spans="1:18" ht="15.75" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>0</v>
       </c>
       <c r="B4" t="s">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="C4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D4" t="str">
         <f t="shared" ref="D4:D12" si="0">_xlfn.CONCAT(B4,":",C4)</f>
         <v>Industrial_roundwood:FI</v>
       </c>
       <c r="E4" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F4">
         <v>0</v>
       </c>
-      <c r="H4" t="s">
-        <v>54</v>
-      </c>
-      <c r="M4" s="4"/>
-      <c r="P4">
+      <c r="G4" t="s">
+        <v>50</v>
+      </c>
+      <c r="J4">
         <v>3.6999999999999998E-2</v>
       </c>
-      <c r="Q4">
+      <c r="K4">
         <v>0.34699999999999998</v>
       </c>
-      <c r="R4" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="5" spans="1:18" ht="15.75" x14ac:dyDescent="0.3">
+      <c r="L4" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>1</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D5" t="str">
         <f t="shared" si="0"/>
         <v>Sawmilling:FI</v>
       </c>
       <c r="E5" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F5">
         <v>0</v>
       </c>
-      <c r="H5" t="s">
-        <v>54</v>
-      </c>
-      <c r="M5" s="4"/>
-      <c r="P5">
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="J5">
         <v>0.24299999999999999</v>
       </c>
-      <c r="Q5">
+      <c r="K5">
         <v>0.39200000000000002</v>
       </c>
-      <c r="R5" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L5" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>2</v>
       </c>
       <c r="B6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D6" t="str">
         <f t="shared" si="0"/>
         <v>Residues:FI</v>
       </c>
       <c r="E6" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="F6">
         <v>0</v>
       </c>
-      <c r="H6" t="s">
-        <v>54</v>
-      </c>
-      <c r="P6">
+      <c r="G6" t="s">
+        <v>50</v>
+      </c>
+      <c r="J6">
         <v>0.40899999999999997</v>
       </c>
-      <c r="Q6">
+      <c r="K6">
         <v>0.05</v>
       </c>
-      <c r="R6" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L6" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>3</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D7" t="str">
         <f t="shared" si="0"/>
         <v>Sawnwood:FI</v>
       </c>
       <c r="E7" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F7">
         <v>0</v>
       </c>
-      <c r="H7" t="s">
-        <v>54</v>
-      </c>
-      <c r="P7">
+      <c r="G7" t="s">
+        <v>50</v>
+      </c>
+      <c r="J7">
         <v>0.40899999999999997</v>
       </c>
-      <c r="Q7">
+      <c r="K7">
         <v>0.53200000000000003</v>
       </c>
-      <c r="R7" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="8" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L7" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>4</v>
       </c>
       <c r="B8" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D8" t="str">
         <f t="shared" si="0"/>
         <v>Construction:FI</v>
       </c>
       <c r="E8" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F8">
         <v>10</v>
       </c>
+      <c r="G8" t="s">
+        <v>35</v>
+      </c>
       <c r="H8" t="s">
-        <v>38</v>
-      </c>
-      <c r="I8" t="s">
-        <v>189</v>
-      </c>
-      <c r="P8">
+        <v>179</v>
+      </c>
+      <c r="J8">
         <v>0.752</v>
       </c>
-      <c r="Q8">
+      <c r="K8">
         <v>0.44400000000000001</v>
       </c>
-      <c r="R8" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="L8" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>5</v>
       </c>
       <c r="B9" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D9" t="str">
         <f t="shared" si="0"/>
         <v>Furniture:FI</v>
       </c>
       <c r="E9" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="F9">
         <v>5</v>
       </c>
+      <c r="G9" t="s">
+        <v>35</v>
+      </c>
       <c r="H9" t="s">
-        <v>38</v>
-      </c>
-      <c r="I9" t="s">
-        <v>189</v>
-      </c>
-      <c r="P9">
+        <v>179</v>
+      </c>
+      <c r="J9">
         <v>0.65600000000000003</v>
       </c>
-      <c r="Q9">
+      <c r="K9">
         <v>0.77300000000000002</v>
       </c>
-      <c r="R9" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L9" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C10" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="D10" t="str">
         <f t="shared" si="0"/>
         <v>Sawnwood:Import</v>
       </c>
       <c r="E10" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F10">
         <v>0</v>
       </c>
-      <c r="H10" t="s">
-        <v>54</v>
-      </c>
-      <c r="P10">
+      <c r="G10" t="s">
+        <v>50</v>
+      </c>
+      <c r="J10">
         <v>0.24299999999999999</v>
       </c>
-      <c r="Q10">
+      <c r="K10">
         <v>0.9</v>
       </c>
-      <c r="R10" t="s">
-        <v>132</v>
-      </c>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L10" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>7</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C11" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="D11" t="str">
         <f t="shared" si="0"/>
         <v>Sawnwood:Export</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F11">
         <v>0</v>
       </c>
-      <c r="H11" t="s">
-        <v>54</v>
-      </c>
-      <c r="P11">
+      <c r="G11" t="s">
+        <v>50</v>
+      </c>
+      <c r="J11">
         <v>0.69099999999999995</v>
       </c>
-      <c r="Q11">
+      <c r="K11">
         <v>0.16500000000000001</v>
       </c>
-      <c r="R11" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.25">
+      <c r="L11" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12">
         <v>8</v>
       </c>
       <c r="B12" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="C12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="D12" t="str">
         <f t="shared" si="0"/>
         <v>Incineration:FI</v>
       </c>
       <c r="E12" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="F12">
         <v>0</v>
       </c>
-      <c r="H12" t="s">
-        <v>54</v>
-      </c>
-      <c r="P12">
+      <c r="G12" t="s">
+        <v>50</v>
+      </c>
+      <c r="J12">
         <v>0.96599999999999997</v>
       </c>
-      <c r="Q12">
+      <c r="K12">
         <v>0.48299999999999998</v>
       </c>
-      <c r="R12" t="s">
-        <v>134</v>
+      <c r="L12" t="s">
+        <v>130</v>
       </c>
     </row>
     <row r="18" ht="15.6" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <dataValidations xWindow="1088" yWindow="385" count="2">
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="see parameters.py for more info" prompt="tuple = number or list of parameters separated by comma. Example: stddev=1. For shape and scale list separated by comma e.g., shape=1, scale=1.5_x000a_Normal: stddev_x000a_LogNormal: stddev_x000a_FoldedNormal: stddev_x000a_Weibull: shape, scale_x000a_LandfillDecayWood /Pap: condition_x000a_" sqref="I4:I1048576" xr:uid="{564AD8C3-F96D-40DD-BFD1-1C6E073701B7}"/>
-    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Sankey diagram positioning" prompt="Sankey diagram X and Y node positioning. Check / adjust positioning after you run case and see coordinates. " sqref="Q2 P4:Q1048576" xr:uid="{167D7519-74A2-4731-8D99-C2A980321CC9}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="see parameters.py for more info" prompt="tuple = number or list of parameters separated by comma. Example: stddev=1. For shape and scale list separated by comma e.g., shape=1, scale=1.5_x000a_Normal: stddev_x000a_LogNormal: stddev_x000a_FoldedNormal: stddev_x000a_Weibull: shape, scale_x000a_LandfillDecayWood /Pap: condition_x000a_" sqref="H4:H1048576" xr:uid="{564AD8C3-F96D-40DD-BFD1-1C6E073701B7}"/>
+    <dataValidation allowBlank="1" showInputMessage="1" showErrorMessage="1" promptTitle="Sankey diagram positioning" prompt="Sankey diagram X and Y node positioning. Check / adjust positioning after you run case and see coordinates. " sqref="K2 J4:K1048576" xr:uid="{167D7519-74A2-4731-8D99-C2A980321CC9}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="4294967293" r:id="rId1"/>
@@ -2648,7 +2553,7 @@
           <x14:formula1>
             <xm:f>'Data validation parameters'!$B$6:$B$14</xm:f>
           </x14:formula1>
-          <xm:sqref>H4:H1048576</xm:sqref>
+          <xm:sqref>G4:G1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -2658,7 +2563,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B692AEE8-68EE-4B81-A49D-50BF066DFFE7}">
-  <dimension ref="A1:P91"/>
+  <dimension ref="A1:N91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
@@ -2673,13 +2578,11 @@
     <col min="10" max="10" width="9.42578125" customWidth="1"/>
     <col min="11" max="11" width="15.85546875" customWidth="1"/>
     <col min="12" max="12" width="12.85546875" customWidth="1"/>
-    <col min="13" max="13" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="21.7109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="15.7109375" customWidth="1"/>
-    <col min="16" max="16" width="42" customWidth="1"/>
+    <col min="13" max="13" width="15.7109375" customWidth="1"/>
+    <col min="14" max="14" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -2717,19 +2620,13 @@
         <v>6</v>
       </c>
       <c r="M1" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="N1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="O1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="P1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
@@ -2743,89 +2640,81 @@
       <c r="I2" s="2"/>
       <c r="J2" s="2"/>
       <c r="K2" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2" t="s">
+        <v>169</v>
+      </c>
+      <c r="N2" s="2"/>
+    </row>
+    <row r="3" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="12" t="s">
+        <v>174</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>157</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="I3" s="6" t="s">
+        <v>162</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>54</v>
+      </c>
+      <c r="K3" s="6" t="s">
+        <v>8</v>
+      </c>
+      <c r="L3" s="6" t="s">
+        <v>23</v>
+      </c>
+      <c r="M3" s="8" t="s">
+        <v>168</v>
+      </c>
+      <c r="N3" s="9" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>40</v>
+      </c>
+      <c r="B4" t="s">
         <v>25</v>
-      </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2"/>
-      <c r="N2" s="2"/>
-      <c r="O2" s="2" t="s">
-        <v>179</v>
-      </c>
-      <c r="P2" s="2"/>
-    </row>
-    <row r="3" spans="1:16" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>184</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>165</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>166</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>167</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>155</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>168</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>169</v>
-      </c>
-      <c r="I3" s="9" t="s">
-        <v>170</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>58</v>
-      </c>
-      <c r="K3" s="9" t="s">
-        <v>8</v>
-      </c>
-      <c r="L3" s="9" t="s">
-        <v>26</v>
-      </c>
-      <c r="M3" s="9" t="s">
-        <v>171</v>
-      </c>
-      <c r="N3" s="10" t="s">
-        <v>172</v>
-      </c>
-      <c r="O3" s="11" t="s">
-        <v>178</v>
-      </c>
-      <c r="P3" s="12" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>44</v>
-      </c>
-      <c r="B4" t="s">
-        <v>28</v>
       </c>
       <c r="C4" t="str">
         <f>+_xlfn.XLOOKUP(H4,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>Source</v>
       </c>
       <c r="D4" t="s">
+        <v>24</v>
+      </c>
+      <c r="E4" t="s">
         <v>27</v>
-      </c>
-      <c r="E4" t="s">
-        <v>30</v>
       </c>
       <c r="F4" t="str">
         <f>+_xlfn.XLOOKUP(I4,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>First</v>
       </c>
       <c r="G4" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H4" s="3" t="str">
         <f t="shared" ref="H4:H13" si="0">_xlfn.CONCAT(B4,":",D4)</f>
@@ -2839,39 +2728,36 @@
         <v>60</v>
       </c>
       <c r="K4" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L4">
         <v>2021</v>
       </c>
-      <c r="N4" t="s">
-        <v>39</v>
-      </c>
-      <c r="P4" s="13"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N4" s="10"/>
+    </row>
+    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>45</v>
+        <v>41</v>
       </c>
       <c r="B5" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C5" t="str">
         <f>+_xlfn.XLOOKUP(H5,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>First</v>
       </c>
       <c r="D5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E5" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F5" t="str">
         <f>+_xlfn.XLOOKUP(I5,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>Second</v>
       </c>
       <c r="G5" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H5" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2890,34 +2776,31 @@
       <c r="L5">
         <v>2021</v>
       </c>
-      <c r="N5" t="s">
-        <v>39</v>
-      </c>
-      <c r="P5" s="13"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N5" s="10"/>
+    </row>
+    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="B6" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="C6" t="str">
         <f>+_xlfn.XLOOKUP(H6,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>First</v>
       </c>
       <c r="D6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E6" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="F6" t="str">
         <f>+_xlfn.XLOOKUP(I6,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>by_prod</v>
       </c>
       <c r="G6" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H6" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2931,39 +2814,36 @@
         <v>10</v>
       </c>
       <c r="K6" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L6">
         <v>2021</v>
       </c>
-      <c r="N6" t="s">
-        <v>39</v>
-      </c>
-      <c r="P6" s="13"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N6" s="10"/>
+    </row>
+    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>51</v>
+        <v>47</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C7" t="str">
         <f>+_xlfn.XLOOKUP(H7,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>Second</v>
       </c>
       <c r="D7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E7" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="F7" t="str">
         <f>+_xlfn.XLOOKUP(I7,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>VAM</v>
       </c>
       <c r="G7" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H7" s="3" t="str">
         <f t="shared" si="0"/>
@@ -2982,36 +2862,33 @@
       <c r="L7">
         <v>2021</v>
       </c>
-      <c r="N7" t="s">
-        <v>39</v>
-      </c>
-      <c r="O7">
+      <c r="M7">
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:16" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="B8" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C8" t="str">
         <f>+_xlfn.XLOOKUP(H8,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>Second</v>
       </c>
       <c r="D8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E8" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="F8" t="str">
         <f>+_xlfn.XLOOKUP(I8,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>VAM</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H8" s="3" t="str">
         <f>_xlfn.CONCAT(B8,":",D8)</f>
@@ -3030,36 +2907,33 @@
       <c r="L8">
         <v>2021</v>
       </c>
-      <c r="N8" t="s">
-        <v>39</v>
-      </c>
-      <c r="O8">
+      <c r="M8">
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="B9" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C9" t="str">
         <f>+_xlfn.XLOOKUP(H9,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>VAM</v>
       </c>
       <c r="D9" t="s">
+        <v>24</v>
+      </c>
+      <c r="E9" t="s">
         <v>27</v>
-      </c>
-      <c r="E9" t="s">
-        <v>30</v>
       </c>
       <c r="F9" t="str">
         <f>+_xlfn.XLOOKUP(I9,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>First</v>
       </c>
       <c r="G9" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H9" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3078,33 +2952,30 @@
       <c r="L9">
         <v>2021</v>
       </c>
-      <c r="N9" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>49</v>
+        <v>45</v>
       </c>
       <c r="B10" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="C10" t="str">
         <f>+_xlfn.XLOOKUP(H10,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>VAM</v>
       </c>
       <c r="D10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E10" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F10" t="str">
         <f>+_xlfn.XLOOKUP(I10,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>EoL</v>
       </c>
       <c r="G10" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H10" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3123,32 +2994,29 @@
       <c r="L10">
         <v>2021</v>
       </c>
-      <c r="N10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="B11" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>34</v>
+        <v>31</v>
       </c>
       <c r="F11" t="str">
         <f>+_xlfn.XLOOKUP(I11,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>EoL</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H11" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3167,34 +3035,31 @@
       <c r="L11">
         <v>2021</v>
       </c>
-      <c r="N11" t="s">
-        <v>39</v>
-      </c>
-      <c r="P11" s="13"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N11" s="10"/>
+    </row>
+    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>52</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C12" t="str">
         <f>+_xlfn.XLOOKUP(H12,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>Second</v>
       </c>
       <c r="D12" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="E12" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F12" t="str">
         <f>+_xlfn.XLOOKUP(I12,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>RoW</v>
       </c>
       <c r="G12" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="H12" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3208,39 +3073,36 @@
         <v>20</v>
       </c>
       <c r="K12" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L12">
         <v>2021</v>
       </c>
-      <c r="N12" t="s">
-        <v>39</v>
-      </c>
-      <c r="P12" s="13"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N12" s="10"/>
+    </row>
+    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>53</v>
+        <v>49</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="C13" t="str">
         <f>+_xlfn.XLOOKUP(H13,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>RoW</v>
       </c>
       <c r="D13" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="E13" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="F13" t="str">
         <f>+_xlfn.XLOOKUP(I13,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
         <v>Second</v>
       </c>
       <c r="G13" t="s">
-        <v>27</v>
+        <v>24</v>
       </c>
       <c r="H13" s="3" t="str">
         <f t="shared" si="0"/>
@@ -3254,401 +3116,330 @@
         <v>10</v>
       </c>
       <c r="K13" t="s">
-        <v>43</v>
+        <v>39</v>
       </c>
       <c r="L13">
         <v>2021</v>
       </c>
-      <c r="N13" t="s">
-        <v>39</v>
-      </c>
-      <c r="P13" s="13"/>
-    </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="N13" s="10"/>
+    </row>
+    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H14" s="3"/>
       <c r="I14" s="3"/>
-      <c r="N14"/>
-    </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H15" s="3"/>
       <c r="I15" s="3"/>
-      <c r="N15"/>
-    </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.25">
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
       <c r="H16" s="3"/>
       <c r="I16" s="3"/>
-      <c r="N16"/>
-    </row>
-    <row r="17" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="17" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H17" s="3"/>
       <c r="I17" s="3"/>
-      <c r="N17"/>
-    </row>
-    <row r="18" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="18" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H18" s="3"/>
       <c r="I18" s="3"/>
-      <c r="N18"/>
-    </row>
-    <row r="19" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="19" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H19" s="3"/>
       <c r="I19" s="3"/>
-      <c r="N19"/>
-    </row>
-    <row r="20" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="20" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H20" s="3"/>
       <c r="I20" s="3"/>
-      <c r="N20"/>
-    </row>
-    <row r="21" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="21" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H21" s="3"/>
       <c r="I21" s="3"/>
-      <c r="N21"/>
-    </row>
-    <row r="22" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="22" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H22" s="3"/>
       <c r="I22" s="3"/>
-      <c r="N22"/>
-    </row>
-    <row r="23" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="23" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H23" s="3"/>
       <c r="I23" s="3"/>
-      <c r="N23"/>
-    </row>
-    <row r="24" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="24" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H24" s="3"/>
       <c r="I24" s="3"/>
     </row>
-    <row r="25" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="25" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H25" s="3"/>
       <c r="I25" s="3"/>
     </row>
-    <row r="26" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="26" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H26" s="3"/>
       <c r="I26" s="3"/>
     </row>
-    <row r="27" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="27" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H27" s="3"/>
       <c r="I27" s="3"/>
     </row>
-    <row r="28" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="28" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H28" s="3"/>
       <c r="I28" s="3"/>
-      <c r="N28" s="6"/>
-    </row>
-    <row r="29" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="29" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H29" s="3"/>
       <c r="I29" s="3"/>
-      <c r="N29" s="6"/>
-    </row>
-    <row r="30" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="30" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H30" s="3"/>
       <c r="I30" s="3"/>
     </row>
-    <row r="31" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="31" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H31" s="3"/>
       <c r="I31" s="3"/>
     </row>
-    <row r="32" spans="8:14" x14ac:dyDescent="0.25">
+    <row r="32" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H32" s="3"/>
       <c r="I32" s="3"/>
     </row>
-    <row r="33" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="33" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H33" s="3"/>
       <c r="I33" s="3"/>
     </row>
-    <row r="34" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="34" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H34" s="3"/>
       <c r="I34" s="3"/>
     </row>
-    <row r="35" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="E35" s="13"/>
+    <row r="35" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="E35" s="10"/>
       <c r="H35" s="3"/>
       <c r="I35" s="3"/>
     </row>
-    <row r="36" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="36" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H36" s="3"/>
       <c r="I36" s="3"/>
     </row>
-    <row r="37" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="37" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H37" s="3"/>
       <c r="I37" s="3"/>
     </row>
-    <row r="38" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="38" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H38" s="3"/>
       <c r="I38" s="3"/>
     </row>
-    <row r="39" spans="3:14" x14ac:dyDescent="0.25">
+    <row r="39" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H39" s="3"/>
       <c r="I39" s="3"/>
-      <c r="N39"/>
-    </row>
-    <row r="40" spans="3:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="40" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H40" s="3"/>
       <c r="I40" s="3"/>
-      <c r="N40"/>
-    </row>
-    <row r="41" spans="3:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="41" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H41" s="3"/>
       <c r="I41" s="3"/>
-      <c r="N41"/>
-    </row>
-    <row r="42" spans="3:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="42" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H42" s="3"/>
       <c r="I42" s="3"/>
-      <c r="N42"/>
-    </row>
-    <row r="43" spans="3:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="43" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H43" s="3"/>
       <c r="I43" s="3"/>
-      <c r="N43"/>
-    </row>
-    <row r="44" spans="3:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="44" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H44" s="3"/>
       <c r="I44" s="3"/>
-      <c r="N44"/>
-    </row>
-    <row r="45" spans="3:14" x14ac:dyDescent="0.25">
-      <c r="C45" s="8"/>
+    </row>
+    <row r="45" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C45" s="5"/>
       <c r="H45" s="3"/>
       <c r="I45" s="3"/>
-      <c r="N45"/>
-    </row>
-    <row r="46" spans="3:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="46" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H46" s="3"/>
       <c r="I46" s="3"/>
-      <c r="N46"/>
-    </row>
-    <row r="47" spans="3:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="47" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H47" s="3"/>
       <c r="I47" s="3"/>
-      <c r="N47"/>
-    </row>
-    <row r="48" spans="3:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="48" spans="3:9" x14ac:dyDescent="0.25">
       <c r="H48" s="3"/>
       <c r="I48" s="3"/>
-      <c r="N48"/>
-    </row>
-    <row r="49" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="49" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H49" s="3"/>
       <c r="I49" s="3"/>
-      <c r="N49"/>
-    </row>
-    <row r="50" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="50" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H50" s="3"/>
       <c r="I50" s="3"/>
-      <c r="N50"/>
-    </row>
-    <row r="51" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="51" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H51" s="3"/>
       <c r="I51" s="3"/>
-      <c r="N51"/>
-    </row>
-    <row r="52" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="52" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H52" s="3"/>
       <c r="I52" s="3"/>
-      <c r="N52"/>
-    </row>
-    <row r="53" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="53" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H53" s="3"/>
       <c r="I53" s="3"/>
-      <c r="N53"/>
-    </row>
-    <row r="54" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="54" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H54" s="3"/>
       <c r="I54" s="3"/>
-      <c r="N54"/>
-    </row>
-    <row r="55" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="55" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H55" s="3"/>
       <c r="I55" s="3"/>
-      <c r="N55"/>
-    </row>
-    <row r="56" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="56" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H56" s="3"/>
       <c r="I56" s="3"/>
-      <c r="N56"/>
-    </row>
-    <row r="57" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="57" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H57" s="3"/>
       <c r="I57" s="3"/>
-      <c r="N57"/>
-    </row>
-    <row r="58" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="58" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H58" s="3"/>
       <c r="I58" s="3"/>
-      <c r="N58"/>
-    </row>
-    <row r="59" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="59" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H59" s="3"/>
       <c r="I59" s="3"/>
-      <c r="N59"/>
-    </row>
-    <row r="60" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="60" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H60" s="3"/>
       <c r="I60" s="3"/>
-      <c r="N60"/>
-    </row>
-    <row r="61" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="61" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H61" s="3"/>
       <c r="I61" s="3"/>
-      <c r="N61"/>
-    </row>
-    <row r="62" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="62" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H62" s="3"/>
       <c r="I62" s="3"/>
-      <c r="N62"/>
-    </row>
-    <row r="63" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="63" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H63" s="3"/>
       <c r="I63" s="3"/>
-      <c r="N63"/>
-    </row>
-    <row r="64" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="64" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H64" s="3"/>
       <c r="I64" s="3"/>
-      <c r="N64"/>
-    </row>
-    <row r="65" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="65" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H65" s="3"/>
       <c r="I65" s="3"/>
-      <c r="N65"/>
-    </row>
-    <row r="66" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="66" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H66" s="3"/>
       <c r="I66" s="3"/>
-      <c r="N66"/>
-    </row>
-    <row r="67" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="67" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H67" s="3"/>
       <c r="I67" s="3"/>
-      <c r="N67"/>
-    </row>
-    <row r="68" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="68" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H68" s="3"/>
       <c r="I68" s="3"/>
-      <c r="N68"/>
-    </row>
-    <row r="69" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="69" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H69" s="3"/>
       <c r="I69" s="3"/>
-      <c r="N69"/>
-    </row>
-    <row r="70" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="70" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H70" s="3"/>
       <c r="I70" s="3"/>
-      <c r="N70"/>
-    </row>
-    <row r="71" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="71" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H71" s="3"/>
       <c r="I71" s="3"/>
-      <c r="N71"/>
-    </row>
-    <row r="72" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="72" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H72" s="3"/>
       <c r="I72" s="3"/>
-      <c r="N72"/>
-    </row>
-    <row r="73" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="73" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H73" s="3"/>
       <c r="I73" s="3"/>
-      <c r="N73"/>
-    </row>
-    <row r="74" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="74" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H74" s="3"/>
       <c r="I74" s="3"/>
-      <c r="N74"/>
-    </row>
-    <row r="75" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="75" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H75" s="3"/>
       <c r="I75" s="3"/>
-      <c r="N75"/>
-    </row>
-    <row r="76" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="76" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H76" s="3"/>
       <c r="I76" s="3"/>
-      <c r="N76"/>
-    </row>
-    <row r="77" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="77" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H77" s="3"/>
       <c r="I77" s="3"/>
-      <c r="N77"/>
-    </row>
-    <row r="78" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="78" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H78" s="3"/>
       <c r="I78" s="3"/>
-      <c r="N78"/>
-    </row>
-    <row r="79" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="79" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H79" s="3"/>
       <c r="I79" s="3"/>
-      <c r="N79"/>
-    </row>
-    <row r="80" spans="8:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="80" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H80" s="3"/>
       <c r="I80" s="3"/>
-      <c r="N80"/>
-    </row>
-    <row r="81" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
       <c r="H81" s="3"/>
       <c r="I81" s="3"/>
-      <c r="N81"/>
-    </row>
-    <row r="82" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
       <c r="H82" s="3"/>
       <c r="I82" s="3"/>
-      <c r="N82"/>
-    </row>
-    <row r="83" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
       <c r="H83" s="3"/>
       <c r="I83" s="3"/>
-      <c r="N83"/>
-    </row>
-    <row r="84" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
       <c r="H84" s="3"/>
       <c r="I84" s="3"/>
-      <c r="N84"/>
-    </row>
-    <row r="85" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
       <c r="H85" s="3"/>
       <c r="I85" s="3"/>
-      <c r="N85"/>
-    </row>
-    <row r="86" spans="2:14" x14ac:dyDescent="0.25">
-      <c r="N86"/>
-    </row>
-    <row r="87" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
       <c r="B87" s="3"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
       <c r="G87" s="3"/>
       <c r="H87" s="3"/>
       <c r="I87" s="3"/>
-      <c r="M87" s="3"/>
-      <c r="N87"/>
-    </row>
-    <row r="88" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
       <c r="H88" s="3"/>
       <c r="I88" s="3"/>
-      <c r="N88"/>
-    </row>
-    <row r="89" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
       <c r="H89" s="3"/>
       <c r="I89" s="3"/>
-      <c r="N89"/>
-    </row>
-    <row r="90" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
       <c r="H90" s="3"/>
       <c r="I90" s="3"/>
-      <c r="N90"/>
-    </row>
-    <row r="91" spans="2:14" x14ac:dyDescent="0.25">
+    </row>
+    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
       <c r="H91" s="3"/>
       <c r="I91" s="3"/>
-      <c r="N91"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:P13" xr:uid="{B692AEE8-68EE-4B81-A49D-50BF066DFFE7}"/>
-  <phoneticPr fontId="5" type="noConversion"/>
+  <autoFilter ref="A3:N13" xr:uid="{B692AEE8-68EE-4B81-A49D-50BF066DFFE7}"/>
+  <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
   <drawing r:id="rId2"/>
@@ -3687,13 +3478,13 @@
         <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>5</v>
@@ -3717,43 +3508,43 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>216</v>
-      </c>
-      <c r="B3" s="9" t="s">
-        <v>42</v>
-      </c>
-      <c r="C3" s="9" t="s">
-        <v>60</v>
-      </c>
-      <c r="D3" s="9" t="s">
-        <v>111</v>
-      </c>
-      <c r="E3" s="9" t="s">
-        <v>112</v>
-      </c>
-      <c r="F3" s="9" t="s">
-        <v>217</v>
-      </c>
-      <c r="G3" s="9" t="s">
-        <v>218</v>
-      </c>
-      <c r="H3" s="9" t="s">
-        <v>219</v>
-      </c>
-      <c r="I3" s="10" t="s">
-        <v>220</v>
-      </c>
-      <c r="J3" s="9" t="s">
-        <v>13</v>
+      <c r="A3" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="B3" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="6" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="6" t="s">
+        <v>207</v>
+      </c>
+      <c r="G3" s="6" t="s">
+        <v>208</v>
+      </c>
+      <c r="H3" s="6" t="s">
+        <v>209</v>
+      </c>
+      <c r="I3" s="7" t="s">
+        <v>210</v>
+      </c>
+      <c r="J3" s="6" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="B4" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -3768,10 +3559,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="B5" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -3785,10 +3576,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="B6" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="D6">
         <v>2026</v>
@@ -3799,10 +3590,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="B7" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -3813,10 +3604,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="B8" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -3830,10 +3621,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>247</v>
+        <v>237</v>
       </c>
       <c r="B9" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -3847,10 +3638,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="B10" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -3861,10 +3652,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="B11" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -3878,10 +3669,10 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="B12" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -3893,15 +3684,15 @@
         <v>1900</v>
       </c>
       <c r="F12" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="B13" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -3913,15 +3704,15 @@
         <v>1900</v>
       </c>
       <c r="G13" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="B14" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -3933,15 +3724,15 @@
         <v>1900</v>
       </c>
       <c r="H14" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="B15" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -3953,7 +3744,7 @@
         <v>1900</v>
       </c>
       <c r="I15" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
     </row>
   </sheetData>
@@ -3991,16 +3782,16 @@
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="B1" t="s">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="C1" t="s">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="D1" t="s">
-        <v>21</v>
+        <v>18</v>
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.25">
@@ -4008,7 +3799,7 @@
         <v>2021</v>
       </c>
       <c r="B2" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C2">
         <v>3.6999999999999998E-2</v>
@@ -4022,7 +3813,7 @@
         <v>2021</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C3">
         <v>0.24299999999999999</v>
@@ -4036,7 +3827,7 @@
         <v>2021</v>
       </c>
       <c r="B4" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C4">
         <v>0.40899999999999997</v>
@@ -4050,7 +3841,7 @@
         <v>2021</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C5">
         <v>0.40899999999999997</v>
@@ -4064,7 +3855,7 @@
         <v>2021</v>
       </c>
       <c r="B6" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C6">
         <v>0.752</v>
@@ -4078,7 +3869,7 @@
         <v>2021</v>
       </c>
       <c r="B7" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C7">
         <v>0.65600000000000003</v>
@@ -4092,7 +3883,7 @@
         <v>2021</v>
       </c>
       <c r="B8" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C8">
         <v>0.96599999999999997</v>
@@ -4106,7 +3897,7 @@
         <v>2021</v>
       </c>
       <c r="B9" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C9">
         <v>0.69099999999999995</v>
@@ -4120,7 +3911,7 @@
         <v>2021</v>
       </c>
       <c r="B10" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C10">
         <v>0.24299999999999999</v>
@@ -4134,7 +3925,7 @@
         <v>2022</v>
       </c>
       <c r="B11" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C11">
         <v>3.6999999999999998E-2</v>
@@ -4148,7 +3939,7 @@
         <v>2022</v>
       </c>
       <c r="B12" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C12">
         <v>0.24299999999999999</v>
@@ -4162,7 +3953,7 @@
         <v>2022</v>
       </c>
       <c r="B13" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C13">
         <v>0.40899999999999997</v>
@@ -4176,7 +3967,7 @@
         <v>2022</v>
       </c>
       <c r="B14" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C14">
         <v>0.40899999999999997</v>
@@ -4190,7 +3981,7 @@
         <v>2022</v>
       </c>
       <c r="B15" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C15">
         <v>0.752</v>
@@ -4204,7 +3995,7 @@
         <v>2022</v>
       </c>
       <c r="B16" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C16">
         <v>0.65600000000000003</v>
@@ -4218,7 +4009,7 @@
         <v>2022</v>
       </c>
       <c r="B17" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C17">
         <v>0.96599999999999997</v>
@@ -4232,7 +4023,7 @@
         <v>2022</v>
       </c>
       <c r="B18" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C18">
         <v>0.69099999999999995</v>
@@ -4246,7 +4037,7 @@
         <v>2022</v>
       </c>
       <c r="B19" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C19">
         <v>0.24299999999999999</v>
@@ -4260,7 +4051,7 @@
         <v>2023</v>
       </c>
       <c r="B20" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C20">
         <v>3.6999999999999998E-2</v>
@@ -4274,7 +4065,7 @@
         <v>2023</v>
       </c>
       <c r="B21" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C21">
         <v>0.24299999999999999</v>
@@ -4288,7 +4079,7 @@
         <v>2023</v>
       </c>
       <c r="B22" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C22">
         <v>0.40899999999999997</v>
@@ -4302,7 +4093,7 @@
         <v>2023</v>
       </c>
       <c r="B23" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C23">
         <v>0.40899999999999997</v>
@@ -4316,7 +4107,7 @@
         <v>2023</v>
       </c>
       <c r="B24" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C24">
         <v>0.752</v>
@@ -4330,7 +4121,7 @@
         <v>2023</v>
       </c>
       <c r="B25" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C25">
         <v>0.65600000000000003</v>
@@ -4344,7 +4135,7 @@
         <v>2023</v>
       </c>
       <c r="B26" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C26">
         <v>0.96599999999999997</v>
@@ -4358,7 +4149,7 @@
         <v>2023</v>
       </c>
       <c r="B27" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C27">
         <v>0.69099999999999995</v>
@@ -4372,7 +4163,7 @@
         <v>2023</v>
       </c>
       <c r="B28" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C28">
         <v>0.24299999999999999</v>
@@ -4386,7 +4177,7 @@
         <v>2024</v>
       </c>
       <c r="B29" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C29">
         <v>3.6999999999999998E-2</v>
@@ -4400,7 +4191,7 @@
         <v>2024</v>
       </c>
       <c r="B30" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C30">
         <v>0.24299999999999999</v>
@@ -4414,7 +4205,7 @@
         <v>2024</v>
       </c>
       <c r="B31" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C31">
         <v>0.40899999999999997</v>
@@ -4428,7 +4219,7 @@
         <v>2024</v>
       </c>
       <c r="B32" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C32">
         <v>0.40899999999999997</v>
@@ -4442,7 +4233,7 @@
         <v>2024</v>
       </c>
       <c r="B33" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C33">
         <v>0.752</v>
@@ -4456,7 +4247,7 @@
         <v>2024</v>
       </c>
       <c r="B34" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C34">
         <v>0.65600000000000003</v>
@@ -4470,7 +4261,7 @@
         <v>2024</v>
       </c>
       <c r="B35" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C35">
         <v>0.96599999999999997</v>
@@ -4484,7 +4275,7 @@
         <v>2024</v>
       </c>
       <c r="B36" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C36">
         <v>0.69099999999999995</v>
@@ -4498,7 +4289,7 @@
         <v>2024</v>
       </c>
       <c r="B37" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C37">
         <v>0.24299999999999999</v>
@@ -4512,7 +4303,7 @@
         <v>2025</v>
       </c>
       <c r="B38" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C38">
         <v>3.6999999999999998E-2</v>
@@ -4526,7 +4317,7 @@
         <v>2025</v>
       </c>
       <c r="B39" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C39">
         <v>0.24299999999999999</v>
@@ -4540,7 +4331,7 @@
         <v>2025</v>
       </c>
       <c r="B40" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C40">
         <v>0.40899999999999997</v>
@@ -4554,7 +4345,7 @@
         <v>2025</v>
       </c>
       <c r="B41" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C41">
         <v>0.40899999999999997</v>
@@ -4568,7 +4359,7 @@
         <v>2025</v>
       </c>
       <c r="B42" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C42">
         <v>0.752</v>
@@ -4582,7 +4373,7 @@
         <v>2025</v>
       </c>
       <c r="B43" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C43">
         <v>0.65600000000000003</v>
@@ -4596,7 +4387,7 @@
         <v>2025</v>
       </c>
       <c r="B44" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C44">
         <v>0.96599999999999997</v>
@@ -4610,7 +4401,7 @@
         <v>2025</v>
       </c>
       <c r="B45" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C45">
         <v>0.69099999999999995</v>
@@ -4624,7 +4415,7 @@
         <v>2025</v>
       </c>
       <c r="B46" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C46">
         <v>0.24299999999999999</v>
@@ -4638,7 +4429,7 @@
         <v>2026</v>
       </c>
       <c r="B47" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C47">
         <v>3.6999999999999998E-2</v>
@@ -4652,7 +4443,7 @@
         <v>2026</v>
       </c>
       <c r="B48" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C48">
         <v>0.24299999999999999</v>
@@ -4666,7 +4457,7 @@
         <v>2026</v>
       </c>
       <c r="B49" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C49">
         <v>0.40899999999999997</v>
@@ -4680,7 +4471,7 @@
         <v>2026</v>
       </c>
       <c r="B50" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C50">
         <v>0.40899999999999997</v>
@@ -4694,7 +4485,7 @@
         <v>2026</v>
       </c>
       <c r="B51" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C51">
         <v>0.752</v>
@@ -4708,7 +4499,7 @@
         <v>2026</v>
       </c>
       <c r="B52" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C52">
         <v>0.65600000000000003</v>
@@ -4722,7 +4513,7 @@
         <v>2026</v>
       </c>
       <c r="B53" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C53">
         <v>0.96599999999999997</v>
@@ -4736,7 +4527,7 @@
         <v>2026</v>
       </c>
       <c r="B54" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C54">
         <v>0.69099999999999995</v>
@@ -4750,7 +4541,7 @@
         <v>2026</v>
       </c>
       <c r="B55" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C55">
         <v>0.24299999999999999</v>
@@ -4764,7 +4555,7 @@
         <v>2027</v>
       </c>
       <c r="B56" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C56">
         <v>3.6999999999999998E-2</v>
@@ -4778,7 +4569,7 @@
         <v>2027</v>
       </c>
       <c r="B57" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C57">
         <v>0.24299999999999999</v>
@@ -4792,7 +4583,7 @@
         <v>2027</v>
       </c>
       <c r="B58" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C58">
         <v>0.40899999999999997</v>
@@ -4806,7 +4597,7 @@
         <v>2027</v>
       </c>
       <c r="B59" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C59">
         <v>0.40899999999999997</v>
@@ -4820,7 +4611,7 @@
         <v>2027</v>
       </c>
       <c r="B60" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C60">
         <v>0.752</v>
@@ -4834,7 +4625,7 @@
         <v>2027</v>
       </c>
       <c r="B61" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C61">
         <v>0.65600000000000003</v>
@@ -4848,7 +4639,7 @@
         <v>2027</v>
       </c>
       <c r="B62" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C62">
         <v>0.96599999999999997</v>
@@ -4862,7 +4653,7 @@
         <v>2027</v>
       </c>
       <c r="B63" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C63">
         <v>0.69099999999999995</v>
@@ -4876,7 +4667,7 @@
         <v>2027</v>
       </c>
       <c r="B64" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C64">
         <v>0.24299999999999999</v>
@@ -4890,7 +4681,7 @@
         <v>2028</v>
       </c>
       <c r="B65" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C65">
         <v>3.6999999999999998E-2</v>
@@ -4904,7 +4695,7 @@
         <v>2028</v>
       </c>
       <c r="B66" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C66">
         <v>0.24299999999999999</v>
@@ -4918,7 +4709,7 @@
         <v>2028</v>
       </c>
       <c r="B67" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C67">
         <v>0.40899999999999997</v>
@@ -4932,7 +4723,7 @@
         <v>2028</v>
       </c>
       <c r="B68" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C68">
         <v>0.40899999999999997</v>
@@ -4946,7 +4737,7 @@
         <v>2028</v>
       </c>
       <c r="B69" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C69">
         <v>0.752</v>
@@ -4960,7 +4751,7 @@
         <v>2028</v>
       </c>
       <c r="B70" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C70">
         <v>0.65600000000000003</v>
@@ -4974,7 +4765,7 @@
         <v>2028</v>
       </c>
       <c r="B71" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C71">
         <v>0.96599999999999997</v>
@@ -4988,7 +4779,7 @@
         <v>2028</v>
       </c>
       <c r="B72" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C72">
         <v>0.69099999999999995</v>
@@ -5002,7 +4793,7 @@
         <v>2028</v>
       </c>
       <c r="B73" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C73">
         <v>0.24299999999999999</v>
@@ -5016,7 +4807,7 @@
         <v>2029</v>
       </c>
       <c r="B74" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C74">
         <v>3.6999999999999998E-2</v>
@@ -5030,7 +4821,7 @@
         <v>2029</v>
       </c>
       <c r="B75" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C75">
         <v>0.24299999999999999</v>
@@ -5044,7 +4835,7 @@
         <v>2029</v>
       </c>
       <c r="B76" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C76">
         <v>0.40899999999999997</v>
@@ -5058,7 +4849,7 @@
         <v>2029</v>
       </c>
       <c r="B77" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C77">
         <v>0.40899999999999997</v>
@@ -5072,7 +4863,7 @@
         <v>2029</v>
       </c>
       <c r="B78" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C78">
         <v>0.752</v>
@@ -5086,7 +4877,7 @@
         <v>2029</v>
       </c>
       <c r="B79" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C79">
         <v>0.65600000000000003</v>
@@ -5100,7 +4891,7 @@
         <v>2029</v>
       </c>
       <c r="B80" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C80">
         <v>0.96599999999999997</v>
@@ -5114,7 +4905,7 @@
         <v>2029</v>
       </c>
       <c r="B81" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C81">
         <v>0.69099999999999995</v>
@@ -5128,7 +4919,7 @@
         <v>2029</v>
       </c>
       <c r="B82" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C82">
         <v>0.24299999999999999</v>
@@ -5142,7 +4933,7 @@
         <v>2030</v>
       </c>
       <c r="B83" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="C83">
         <v>3.6999999999999998E-2</v>
@@ -5156,7 +4947,7 @@
         <v>2030</v>
       </c>
       <c r="B84" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C84">
         <v>0.24299999999999999</v>
@@ -5170,7 +4961,7 @@
         <v>2030</v>
       </c>
       <c r="B85" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="C85">
         <v>0.40899999999999997</v>
@@ -5184,7 +4975,7 @@
         <v>2030</v>
       </c>
       <c r="B86" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C86">
         <v>0.40899999999999997</v>
@@ -5198,7 +4989,7 @@
         <v>2030</v>
       </c>
       <c r="B87" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="C87">
         <v>0.752</v>
@@ -5212,7 +5003,7 @@
         <v>2030</v>
       </c>
       <c r="B88" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="C88">
         <v>0.65600000000000003</v>
@@ -5226,7 +5017,7 @@
         <v>2030</v>
       </c>
       <c r="B89" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="C89">
         <v>0.96599999999999997</v>
@@ -5240,7 +5031,7 @@
         <v>2030</v>
       </c>
       <c r="B90" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="C90">
         <v>0.69099999999999995</v>
@@ -5254,7 +5045,7 @@
         <v>2030</v>
       </c>
       <c r="B91" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C91">
         <v>0.24299999999999999</v>
@@ -5287,52 +5078,52 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="25" t="s">
+      <c r="A1" s="22" t="s">
+        <v>102</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>103</v>
+      </c>
+      <c r="C1" s="22" t="s">
+        <v>104</v>
+      </c>
+      <c r="D1" s="22" t="s">
+        <v>105</v>
+      </c>
+      <c r="E1" s="22" t="s">
+        <v>177</v>
+      </c>
+      <c r="F1" s="22" t="s">
         <v>106</v>
       </c>
-      <c r="B1" s="25" t="s">
+      <c r="G1" s="22" t="s">
         <v>107</v>
       </c>
-      <c r="C1" s="25" t="s">
+      <c r="H1" s="22" t="s">
         <v>108</v>
       </c>
-      <c r="D1" s="25" t="s">
+      <c r="I1" s="22" t="s">
         <v>109</v>
       </c>
-      <c r="E1" s="25" t="s">
-        <v>187</v>
-      </c>
-      <c r="F1" s="25" t="s">
+      <c r="J1" s="22" t="s">
+        <v>199</v>
+      </c>
+      <c r="K1" s="22" t="s">
         <v>110</v>
       </c>
-      <c r="G1" s="25" t="s">
-        <v>111</v>
-      </c>
-      <c r="H1" s="25" t="s">
-        <v>112</v>
-      </c>
-      <c r="I1" s="25" t="s">
-        <v>113</v>
-      </c>
-      <c r="J1" s="25" t="s">
-        <v>209</v>
-      </c>
-      <c r="K1" s="25" t="s">
-        <v>114</v>
-      </c>
-      <c r="L1" s="25" t="s">
-        <v>114</v>
+      <c r="L1" s="22" t="s">
+        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="D2">
         <v>-50</v>
@@ -5347,9 +5138,9 @@
         <v>2030</v>
       </c>
       <c r="I2" t="s">
-        <v>120</v>
-      </c>
-      <c r="J2" s="24" t="b">
+        <v>116</v>
+      </c>
+      <c r="J2" s="21" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5404,77 +5195,77 @@
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
     </row>
     <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="B2" t="s">
-        <v>146</v>
+        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B4" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="B5" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="B7" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="B8" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="B9" t="s">
+        <v>141</v>
+      </c>
+      <c r="C9" t="s">
         <v>145</v>
-      </c>
-      <c r="C9" t="s">
-        <v>149</v>
       </c>
     </row>
   </sheetData>
@@ -5500,126 +5291,126 @@
   <sheetData>
     <row r="2" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B2" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B3" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="C5" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="D5" s="18" t="s">
-        <v>94</v>
-      </c>
-      <c r="E5" s="18" t="s">
-        <v>118</v>
-      </c>
-      <c r="F5" s="18" t="s">
-        <v>113</v>
-      </c>
-      <c r="G5" s="18" t="s">
-        <v>195</v>
-      </c>
-      <c r="H5" s="18" t="s">
-        <v>221</v>
+      <c r="B5" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="C5" s="15" t="s">
+        <v>69</v>
+      </c>
+      <c r="D5" s="15" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>114</v>
+      </c>
+      <c r="F5" s="15" t="s">
+        <v>109</v>
+      </c>
+      <c r="G5" s="15" t="s">
+        <v>185</v>
+      </c>
+      <c r="H5" s="15" t="s">
+        <v>211</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B6" t="s">
-        <v>54</v>
+        <v>50</v>
       </c>
       <c r="C6" t="b">
         <v>1</v>
       </c>
       <c r="D6" t="s">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="E6" t="s">
-        <v>58</v>
+        <v>54</v>
       </c>
       <c r="F6" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="G6" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="H6" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>38</v>
+        <v>35</v>
       </c>
       <c r="C7" t="b">
         <v>0</v>
       </c>
       <c r="D7" t="s">
-        <v>96</v>
+        <v>92</v>
       </c>
       <c r="E7" t="s">
         <v>9</v>
       </c>
       <c r="F7" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="G7" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="H7" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>55</v>
+        <v>51</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>93</v>
       </c>
       <c r="F8" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="H8" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>57</v>
+        <v>53</v>
       </c>
       <c r="D9" t="s">
-        <v>98</v>
+        <v>94</v>
       </c>
       <c r="F9" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
     </row>
     <row r="10" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>56</v>
+        <v>52</v>
       </c>
     </row>
     <row r="11" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>99</v>
+        <v>95</v>
       </c>
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
     </row>
   </sheetData>
@@ -5629,27 +5420,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="145cc194-9bea-4db6-b116-a042a4529fcd" xsi:nil="true"/>
-    <Comment xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Asiakirja" ma:contentTypeID="0x010100806C55B750152A459818B636E97A41C3" ma:contentTypeVersion="19" ma:contentTypeDescription="Luo uusi asiakirja." ma:contentTypeScope="" ma:versionID="74fd9cb75cef04cf26a1ff9ddef01b4b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xmlns:ns3="145cc194-9bea-4db6-b116-a042a4529fcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="afbcbfdd38894bc2ff0644b00c8ec680" ns2:_="" ns3:_="">
     <xsd:import namespace="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
@@ -5912,32 +5682,28 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557FAA9C-B184-448F-B58D-00E4D46BDD72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="145cc194-9bea-4db6-b116-a042a4529fcd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="145cc194-9bea-4db6-b116-a042a4529fcd" xsi:nil="true"/>
+    <Comment xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
 </file>
 
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60021C7-CA75-4673-96EA-55284BF81134}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5954,4 +5720,29 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557FAA9C-B184-448F-B58D-00E4D46BDD72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="145cc194-9bea-4db6-b116-a042a4529fcd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
--- a/tests/reference_data/test_scenario_stock_lt_overrides.xlsx
+++ b/tests/reference_data/test_scenario_stock_lt_overrides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\PythonProjects\aiphoria\tests\reference_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B6C6F6-3283-40C7-AD05-DAA25C06FB7F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C5CEC2-46F8-4A6F-8819-0E154B357229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-22890" yWindow="3600" windowWidth="21600" windowHeight="11295" activeTab="2" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="11" r:id="rId1"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="525" uniqueCount="244">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="246">
   <si>
     <t>Years</t>
   </si>
@@ -825,6 +825,12 @@
   </si>
   <si>
     <t>Invalid condition</t>
+  </si>
+  <si>
+    <t>version</t>
+  </si>
+  <si>
+    <t>Scenario file format version</t>
   </si>
 </sst>
 </file>
@@ -1464,7 +1470,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{89FFA668-DA1A-459B-BD42-D0D7F7709F0D}">
-  <dimension ref="A2:E41"/>
+  <dimension ref="A2:E42"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="8.7109375" bestFit="1" customWidth="1"/>
@@ -1508,173 +1514,170 @@
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="20" t="s">
-        <v>1</v>
+        <v>244</v>
+      </c>
+      <c r="C7" s="19">
+        <v>2</v>
       </c>
       <c r="D7" s="20" t="s">
         <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>228</v>
+        <v>245</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
-        <v>146</v>
-      </c>
-      <c r="C8" t="s">
-        <v>172</v>
-      </c>
-      <c r="D8" t="s">
-        <v>121</v>
+        <v>60</v>
+      </c>
+      <c r="C8" s="20" t="s">
+        <v>1</v>
+      </c>
+      <c r="D8" s="20" t="s">
+        <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>148</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B9" t="s">
-        <v>61</v>
-      </c>
-      <c r="C9" s="19">
-        <v>2</v>
-      </c>
-      <c r="D9" s="19" t="s">
-        <v>86</v>
+        <v>146</v>
+      </c>
+      <c r="C9" t="s">
+        <v>172</v>
+      </c>
+      <c r="D9" t="s">
+        <v>121</v>
       </c>
       <c r="E9" t="s">
-        <v>64</v>
+        <v>148</v>
       </c>
     </row>
     <row r="10" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B10" t="s">
-        <v>62</v>
-      </c>
-      <c r="C10" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="C10" s="19">
         <v>2</v>
       </c>
-      <c r="D10" s="20" t="s">
-        <v>87</v>
+      <c r="D10" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="E10" t="s">
-        <v>227</v>
+        <v>64</v>
       </c>
     </row>
     <row r="11" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B11" t="s">
-        <v>147</v>
-      </c>
-      <c r="C11" t="s">
-        <v>172</v>
-      </c>
-      <c r="D11" t="s">
-        <v>121</v>
+        <v>62</v>
+      </c>
+      <c r="C11" s="20" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="20" t="s">
+        <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>149</v>
+        <v>227</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>63</v>
-      </c>
-      <c r="C12" s="19">
-        <v>2</v>
-      </c>
-      <c r="D12" s="19" t="s">
-        <v>86</v>
+        <v>147</v>
+      </c>
+      <c r="C12" t="s">
+        <v>172</v>
+      </c>
+      <c r="D12" t="s">
+        <v>121</v>
       </c>
       <c r="E12" t="s">
-        <v>64</v>
+        <v>149</v>
       </c>
     </row>
     <row r="13" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C13" s="19">
-        <v>2021</v>
+        <v>2</v>
       </c>
       <c r="D13" s="19" t="s">
         <v>86</v>
       </c>
       <c r="E13" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
     </row>
     <row r="14" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B14" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C14" s="19">
-        <v>2030</v>
+        <v>2021</v>
       </c>
       <c r="D14" s="19" t="s">
         <v>86</v>
       </c>
       <c r="E14" t="s">
-        <v>75</v>
+        <v>66</v>
       </c>
     </row>
     <row r="15" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B15" t="s">
-        <v>68</v>
-      </c>
-      <c r="C15" s="21" t="b">
-        <v>0</v>
-      </c>
-      <c r="D15" t="s">
-        <v>85</v>
+        <v>67</v>
+      </c>
+      <c r="C15" s="19">
+        <v>2030</v>
+      </c>
+      <c r="D15" s="19" t="s">
+        <v>86</v>
       </c>
       <c r="E15" t="s">
-        <v>70</v>
+        <v>75</v>
       </c>
     </row>
     <row r="16" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B16" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="C16" s="21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="D16" t="s">
         <v>85</v>
       </c>
       <c r="E16" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="B17" t="s">
+        <v>71</v>
+      </c>
+      <c r="C17" s="21" t="b">
+        <v>1</v>
+      </c>
+      <c r="D17" t="s">
+        <v>85</v>
+      </c>
+      <c r="E17" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="B18" t="s">
         <v>79</v>
       </c>
-      <c r="C17" s="11">
+      <c r="C18" s="11">
         <v>0.1</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D18" s="19" t="s">
         <v>89</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E18" t="s">
         <v>80</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>189</v>
-      </c>
-      <c r="B18" t="s">
-        <v>163</v>
-      </c>
-      <c r="C18" t="s">
-        <v>171</v>
-      </c>
-      <c r="D18" t="s">
-        <v>87</v>
-      </c>
-      <c r="E18" t="s">
-        <v>166</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
@@ -1682,16 +1685,16 @@
         <v>189</v>
       </c>
       <c r="B19" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="C19" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="D19" t="s">
         <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
@@ -1699,16 +1702,16 @@
         <v>189</v>
       </c>
       <c r="B20" t="s">
-        <v>73</v>
-      </c>
-      <c r="C20" s="17">
-        <v>-3.6666666666666701</v>
-      </c>
-      <c r="D20" s="17" t="s">
-        <v>89</v>
+        <v>164</v>
+      </c>
+      <c r="C20" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" t="s">
+        <v>87</v>
       </c>
       <c r="E20" t="s">
-        <v>74</v>
+        <v>165</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
@@ -1716,16 +1719,16 @@
         <v>189</v>
       </c>
       <c r="B21" t="s">
-        <v>83</v>
-      </c>
-      <c r="C21" s="21" t="b">
-        <v>1</v>
-      </c>
-      <c r="D21" t="s">
-        <v>85</v>
+        <v>73</v>
+      </c>
+      <c r="C21" s="17">
+        <v>-3.6666666666666701</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>89</v>
       </c>
       <c r="E21" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
@@ -1733,7 +1736,7 @@
         <v>189</v>
       </c>
       <c r="B22" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C22" s="21" t="b">
         <v>1</v>
@@ -1750,16 +1753,16 @@
         <v>189</v>
       </c>
       <c r="B23" t="s">
-        <v>90</v>
-      </c>
-      <c r="C23" t="s">
-        <v>93</v>
+        <v>82</v>
+      </c>
+      <c r="C23" s="21" t="b">
+        <v>1</v>
       </c>
       <c r="D23" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E23" t="s">
-        <v>111</v>
+        <v>84</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
@@ -1767,16 +1770,16 @@
         <v>189</v>
       </c>
       <c r="B24" t="s">
-        <v>175</v>
-      </c>
-      <c r="C24" s="21" t="b">
-        <v>1</v>
+        <v>90</v>
+      </c>
+      <c r="C24" t="s">
+        <v>93</v>
       </c>
       <c r="D24" t="s">
-        <v>85</v>
+        <v>88</v>
       </c>
       <c r="E24" t="s">
-        <v>176</v>
+        <v>111</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
@@ -1784,16 +1787,16 @@
         <v>189</v>
       </c>
       <c r="B25" t="s">
-        <v>184</v>
-      </c>
-      <c r="C25" t="s">
-        <v>186</v>
+        <v>175</v>
+      </c>
+      <c r="C25" s="21" t="b">
+        <v>1</v>
       </c>
       <c r="D25" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="E25" t="s">
-        <v>188</v>
+        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
@@ -1801,16 +1804,16 @@
         <v>189</v>
       </c>
       <c r="B26" t="s">
-        <v>96</v>
+        <v>184</v>
       </c>
       <c r="C26" t="s">
-        <v>97</v>
+        <v>186</v>
       </c>
       <c r="D26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="E26" t="s">
-        <v>226</v>
+        <v>188</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
@@ -1818,13 +1821,16 @@
         <v>189</v>
       </c>
       <c r="B27" t="s">
-        <v>153</v>
+        <v>96</v>
+      </c>
+      <c r="C27" t="s">
+        <v>97</v>
       </c>
       <c r="D27" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="E27" t="s">
-        <v>155</v>
+        <v>226</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
@@ -1832,16 +1838,13 @@
         <v>189</v>
       </c>
       <c r="B28" t="s">
-        <v>98</v>
-      </c>
-      <c r="C28" s="21" t="b">
-        <v>1</v>
+        <v>153</v>
       </c>
       <c r="D28" t="s">
-        <v>85</v>
+        <v>121</v>
       </c>
       <c r="E28" t="s">
-        <v>99</v>
+        <v>155</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
@@ -1849,7 +1852,7 @@
         <v>189</v>
       </c>
       <c r="B29" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="C29" s="21" t="b">
         <v>1</v>
@@ -1858,7 +1861,7 @@
         <v>85</v>
       </c>
       <c r="E29" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
@@ -1866,16 +1869,16 @@
         <v>189</v>
       </c>
       <c r="B30" t="s">
-        <v>119</v>
-      </c>
-      <c r="C30" t="s">
-        <v>122</v>
+        <v>100</v>
+      </c>
+      <c r="C30" s="21" t="b">
+        <v>1</v>
       </c>
       <c r="D30" t="s">
-        <v>121</v>
+        <v>85</v>
       </c>
       <c r="E30" t="s">
-        <v>120</v>
+        <v>101</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
@@ -1883,16 +1886,16 @@
         <v>189</v>
       </c>
       <c r="B31" t="s">
-        <v>139</v>
-      </c>
-      <c r="C31" s="19" t="s">
-        <v>140</v>
-      </c>
-      <c r="D31" s="19" t="s">
-        <v>87</v>
+        <v>119</v>
+      </c>
+      <c r="C31" t="s">
+        <v>122</v>
+      </c>
+      <c r="D31" t="s">
+        <v>121</v>
       </c>
       <c r="E31" t="s">
-        <v>225</v>
+        <v>120</v>
       </c>
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
@@ -1900,41 +1903,44 @@
         <v>189</v>
       </c>
       <c r="B32" t="s">
-        <v>154</v>
-      </c>
-      <c r="D32" t="s">
-        <v>121</v>
+        <v>139</v>
+      </c>
+      <c r="C32" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="D32" s="19" t="s">
+        <v>87</v>
       </c>
       <c r="E32" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>189</v>
       </c>
       <c r="B33" t="s">
-        <v>178</v>
+        <v>154</v>
       </c>
       <c r="D33" t="s">
         <v>121</v>
       </c>
       <c r="E33" t="s">
-        <v>181</v>
-      </c>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>189</v>
       </c>
       <c r="B34" t="s">
-        <v>229</v>
+        <v>178</v>
       </c>
       <c r="D34" t="s">
         <v>121</v>
       </c>
       <c r="E34" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
@@ -1942,16 +1948,13 @@
         <v>189</v>
       </c>
       <c r="B35" t="s">
-        <v>190</v>
-      </c>
-      <c r="C35" t="s">
-        <v>191</v>
+        <v>229</v>
       </c>
       <c r="D35" t="s">
-        <v>87</v>
+        <v>121</v>
       </c>
       <c r="E35" t="s">
-        <v>224</v>
+        <v>180</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
@@ -1959,16 +1962,16 @@
         <v>189</v>
       </c>
       <c r="B36" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="C36" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="D36" t="s">
         <v>87</v>
       </c>
       <c r="E36" t="s">
-        <v>202</v>
+        <v>224</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
@@ -1976,16 +1979,16 @@
         <v>189</v>
       </c>
       <c r="B37" t="s">
-        <v>203</v>
-      </c>
-      <c r="C37" s="21" t="b">
-        <v>1</v>
+        <v>200</v>
+      </c>
+      <c r="C37" t="s">
+        <v>201</v>
       </c>
       <c r="D37" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E37" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
@@ -1993,7 +1996,7 @@
         <v>189</v>
       </c>
       <c r="B38" t="s">
-        <v>215</v>
+        <v>203</v>
       </c>
       <c r="C38" s="21" t="b">
         <v>1</v>
@@ -2002,7 +2005,7 @@
         <v>85</v>
       </c>
       <c r="E38" t="s">
-        <v>216</v>
+        <v>204</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
@@ -2010,16 +2013,16 @@
         <v>189</v>
       </c>
       <c r="B39" t="s">
-        <v>217</v>
-      </c>
-      <c r="C39" t="s">
-        <v>218</v>
+        <v>215</v>
+      </c>
+      <c r="C39" s="21" t="b">
+        <v>1</v>
       </c>
       <c r="D39" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="E39" t="s">
-        <v>223</v>
+        <v>216</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
@@ -2027,16 +2030,16 @@
         <v>189</v>
       </c>
       <c r="B40" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="C40" t="s">
-        <v>172</v>
+        <v>218</v>
       </c>
       <c r="D40" t="s">
-        <v>121</v>
+        <v>87</v>
       </c>
       <c r="E40" t="s">
-        <v>220</v>
+        <v>223</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
@@ -2044,21 +2047,38 @@
         <v>189</v>
       </c>
       <c r="B41" t="s">
+        <v>219</v>
+      </c>
+      <c r="C41" t="s">
+        <v>172</v>
+      </c>
+      <c r="D41" t="s">
+        <v>121</v>
+      </c>
+      <c r="E41" t="s">
+        <v>220</v>
+      </c>
+    </row>
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="A42" t="s">
+        <v>189</v>
+      </c>
+      <c r="B42" t="s">
         <v>221</v>
       </c>
-      <c r="C41">
+      <c r="C42">
         <v>2</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>86</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E42" t="s">
         <v>222</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="B6:E6" xr:uid="{89FFA668-DA1A-459B-BD42-D0D7F7709F0D}"/>
-  <conditionalFormatting sqref="C15:C16">
+  <conditionalFormatting sqref="C16:C17">
     <cfRule type="cellIs" dxfId="11" priority="11" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
@@ -2066,7 +2086,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C21:C22">
+  <conditionalFormatting sqref="C22:C23">
     <cfRule type="cellIs" dxfId="9" priority="9" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
@@ -2074,7 +2094,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24">
+  <conditionalFormatting sqref="C25">
     <cfRule type="cellIs" dxfId="7" priority="5" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
@@ -2082,7 +2102,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C28:C29">
+  <conditionalFormatting sqref="C29:C30">
     <cfRule type="cellIs" dxfId="5" priority="7" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
@@ -2090,7 +2110,7 @@
       <formula>TRUE</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C37:C38">
+  <conditionalFormatting sqref="C38:C39">
     <cfRule type="cellIs" dxfId="3" priority="3" operator="equal">
       <formula>TRUE</formula>
     </cfRule>
@@ -2099,7 +2119,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C15:C16 C21:C22 C28:C29 C24 C37:C38" xr:uid="{79A7E31C-3284-4405-9B5F-03E099B07563}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C16:C17 C22:C23 C29:C30 C25 C38:C39" xr:uid="{79A7E31C-3284-4405-9B5F-03E099B07563}">
       <formula1>Boolean</formula1>
     </dataValidation>
   </dataValidations>
@@ -2112,13 +2132,13 @@
           <x14:formula1>
             <xm:f>'Data validation parameters'!$D$6:$D$9</xm:f>
           </x14:formula1>
-          <xm:sqref>C23</xm:sqref>
+          <xm:sqref>C24</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{7A04E2A2-4928-4E28-9F6D-7D556381B8E8}">
           <x14:formula1>
             <xm:f>'Data validation parameters'!$G$6:$G$7</xm:f>
           </x14:formula1>
-          <xm:sqref>C25</xm:sqref>
+          <xm:sqref>C26</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -5420,6 +5440,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+    <TaxCatchAll xmlns="145cc194-9bea-4db6-b116-a042a4529fcd" xsi:nil="true"/>
+    <Comment xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Asiakirja" ma:contentTypeID="0x010100806C55B750152A459818B636E97A41C3" ma:contentTypeVersion="19" ma:contentTypeDescription="Luo uusi asiakirja." ma:contentTypeScope="" ma:versionID="74fd9cb75cef04cf26a1ff9ddef01b4b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xmlns:ns3="145cc194-9bea-4db6-b116-a042a4529fcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="afbcbfdd38894bc2ff0644b00c8ec680" ns2:_="" ns3:_="">
     <xsd:import namespace="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
@@ -5682,28 +5723,32 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557FAA9C-B184-448F-B58D-00E4D46BDD72}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="145cc194-9bea-4db6-b116-a042a4529fcd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-    <TaxCatchAll xmlns="145cc194-9bea-4db6-b116-a042a4529fcd" xsi:nil="true"/>
-    <Comment xmlns="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xsi:nil="true"/>
-  </documentManagement>
-</p:properties>
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
-<file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60021C7-CA75-4673-96EA-55284BF81134}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5720,29 +5765,4 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557FAA9C-B184-448F-B58D-00E4D46BDD72}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="145cc194-9bea-4db6-b116-a042a4529fcd"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
 </file>
--- a/tests/reference_data/test_scenario_stock_lt_overrides.xlsx
+++ b/tests/reference_data/test_scenario_stock_lt_overrides.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\dev\PythonProjects\aiphoria\tests\reference_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1C5CEC2-46F8-4A6F-8819-0E154B357229}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5249F80A-A957-4009-967D-DB99BA379E7A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{1000A452-A98F-45C1-B843-91F7F67E097C}"/>
   </bookViews>
   <sheets>
     <sheet name="Settings" sheetId="11" r:id="rId1"/>
@@ -23,7 +23,7 @@
     <sheet name="Data validation parameters" sheetId="9" r:id="rId8"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flows!$A$3:$N$13</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">Flows!$A$3:$H$13</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Processes!$D$3:$L$3</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Settings!$B$6:$E$6</definedName>
     <definedName name="Boolean">'Data validation parameters'!$C$6:$C$7</definedName>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="246">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="495" uniqueCount="242">
   <si>
     <t>Years</t>
   </si>
@@ -564,18 +564,6 @@
   </si>
   <si>
     <t>Ignore Excel columns defined in the list when reading data from Colors sheet. Each column name must be separated by comma (',')</t>
-  </si>
-  <si>
-    <t>Source process</t>
-  </si>
-  <si>
-    <t>Source process location</t>
-  </si>
-  <si>
-    <t>Target process</t>
-  </si>
-  <si>
-    <t>Target process location</t>
   </si>
   <si>
     <t>Source ID</t>
@@ -974,13 +962,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="23">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -1128,14 +1115,14 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>549330</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
       <xdr:row>15</xdr:row>
       <xdr:rowOff>64113</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>202129</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>1948324</xdr:colOff>
       <xdr:row>31</xdr:row>
       <xdr:rowOff>167367</xdr:rowOff>
     </xdr:to>
@@ -1481,12 +1468,12 @@
   </cols>
   <sheetData>
     <row r="2" spans="2:5" ht="21" x14ac:dyDescent="0.35">
-      <c r="B2" s="16" t="s">
+      <c r="B2" s="15" t="s">
         <v>58</v>
       </c>
     </row>
     <row r="3" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="17" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1494,50 +1481,50 @@
       <c r="B4" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="18"/>
-      <c r="D4" s="18"/>
-      <c r="E4" s="18"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
     </row>
     <row r="6" spans="2:5" x14ac:dyDescent="0.25">
-      <c r="B6" s="6" t="s">
+      <c r="B6" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="C6" s="6" t="s">
+      <c r="C6" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="D6" s="6" t="s">
+      <c r="D6" s="5" t="s">
         <v>78</v>
       </c>
-      <c r="E6" s="6" t="s">
+      <c r="E6" s="5" t="s">
         <v>3</v>
       </c>
     </row>
     <row r="7" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B7" t="s">
-        <v>244</v>
-      </c>
-      <c r="C7" s="19">
+        <v>240</v>
+      </c>
+      <c r="C7" s="18">
         <v>2</v>
       </c>
-      <c r="D7" s="20" t="s">
+      <c r="D7" s="19" t="s">
         <v>88</v>
       </c>
       <c r="E7" t="s">
-        <v>245</v>
+        <v>241</v>
       </c>
     </row>
     <row r="8" spans="2:5" x14ac:dyDescent="0.25">
       <c r="B8" t="s">
         <v>60</v>
       </c>
-      <c r="C8" s="20" t="s">
+      <c r="C8" s="19" t="s">
         <v>1</v>
       </c>
-      <c r="D8" s="20" t="s">
+      <c r="D8" s="19" t="s">
         <v>88</v>
       </c>
       <c r="E8" t="s">
-        <v>228</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="2:5" x14ac:dyDescent="0.25">
@@ -1545,7 +1532,7 @@
         <v>146</v>
       </c>
       <c r="C9" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D9" t="s">
         <v>121</v>
@@ -1558,10 +1545,10 @@
       <c r="B10" t="s">
         <v>61</v>
       </c>
-      <c r="C10" s="19">
+      <c r="C10" s="18">
         <v>2</v>
       </c>
-      <c r="D10" s="19" t="s">
+      <c r="D10" s="18" t="s">
         <v>86</v>
       </c>
       <c r="E10" t="s">
@@ -1572,14 +1559,14 @@
       <c r="B11" t="s">
         <v>62</v>
       </c>
-      <c r="C11" s="20" t="s">
+      <c r="C11" s="19" t="s">
         <v>2</v>
       </c>
-      <c r="D11" s="20" t="s">
+      <c r="D11" s="19" t="s">
         <v>87</v>
       </c>
       <c r="E11" t="s">
-        <v>227</v>
+        <v>223</v>
       </c>
     </row>
     <row r="12" spans="2:5" x14ac:dyDescent="0.25">
@@ -1587,7 +1574,7 @@
         <v>147</v>
       </c>
       <c r="C12" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D12" t="s">
         <v>121</v>
@@ -1600,10 +1587,10 @@
       <c r="B13" t="s">
         <v>63</v>
       </c>
-      <c r="C13" s="19">
+      <c r="C13" s="18">
         <v>2</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="18" t="s">
         <v>86</v>
       </c>
       <c r="E13" t="s">
@@ -1614,10 +1601,10 @@
       <c r="B14" t="s">
         <v>65</v>
       </c>
-      <c r="C14" s="19">
+      <c r="C14" s="18">
         <v>2021</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="18" t="s">
         <v>86</v>
       </c>
       <c r="E14" t="s">
@@ -1628,10 +1615,10 @@
       <c r="B15" t="s">
         <v>67</v>
       </c>
-      <c r="C15" s="19">
+      <c r="C15" s="18">
         <v>2030</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="18" t="s">
         <v>86</v>
       </c>
       <c r="E15" t="s">
@@ -1642,7 +1629,7 @@
       <c r="B16" t="s">
         <v>68</v>
       </c>
-      <c r="C16" s="21" t="b">
+      <c r="C16" s="20" t="b">
         <v>0</v>
       </c>
       <c r="D16" t="s">
@@ -1656,7 +1643,7 @@
       <c r="B17" t="s">
         <v>71</v>
       </c>
-      <c r="C17" s="21" t="b">
+      <c r="C17" s="20" t="b">
         <v>1</v>
       </c>
       <c r="D17" t="s">
@@ -1670,10 +1657,10 @@
       <c r="B18" t="s">
         <v>79</v>
       </c>
-      <c r="C18" s="11">
+      <c r="C18" s="10">
         <v>0.1</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="18" t="s">
         <v>89</v>
       </c>
       <c r="E18" t="s">
@@ -1682,49 +1669,49 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B19" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="C19" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="D19" t="s">
         <v>87</v>
       </c>
       <c r="E19" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B20" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="C20" t="s">
-        <v>167</v>
+        <v>163</v>
       </c>
       <c r="D20" t="s">
         <v>87</v>
       </c>
       <c r="E20" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B21" t="s">
         <v>73</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="16">
         <v>-3.6666666666666701</v>
       </c>
-      <c r="D21" s="17" t="s">
+      <c r="D21" s="16" t="s">
         <v>89</v>
       </c>
       <c r="E21" t="s">
@@ -1733,12 +1720,12 @@
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B22" t="s">
         <v>83</v>
       </c>
-      <c r="C22" s="21" t="b">
+      <c r="C22" s="20" t="b">
         <v>1</v>
       </c>
       <c r="D22" t="s">
@@ -1750,12 +1737,12 @@
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B23" t="s">
         <v>82</v>
       </c>
-      <c r="C23" s="21" t="b">
+      <c r="C23" s="20" t="b">
         <v>1</v>
       </c>
       <c r="D23" t="s">
@@ -1767,7 +1754,7 @@
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B24" t="s">
         <v>90</v>
@@ -1784,41 +1771,41 @@
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B25" t="s">
-        <v>175</v>
-      </c>
-      <c r="C25" s="21" t="b">
+        <v>171</v>
+      </c>
+      <c r="C25" s="20" t="b">
         <v>1</v>
       </c>
       <c r="D25" t="s">
         <v>85</v>
       </c>
       <c r="E25" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B26" t="s">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="C26" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="D26" t="s">
         <v>88</v>
       </c>
       <c r="E26" t="s">
-        <v>188</v>
+        <v>184</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B27" t="s">
         <v>96</v>
@@ -1830,12 +1817,12 @@
         <v>87</v>
       </c>
       <c r="E27" t="s">
-        <v>226</v>
+        <v>222</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B28" t="s">
         <v>153</v>
@@ -1849,12 +1836,12 @@
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B29" t="s">
         <v>98</v>
       </c>
-      <c r="C29" s="21" t="b">
+      <c r="C29" s="20" t="b">
         <v>1</v>
       </c>
       <c r="D29" t="s">
@@ -1866,12 +1853,12 @@
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B30" t="s">
         <v>100</v>
       </c>
-      <c r="C30" s="21" t="b">
+      <c r="C30" s="20" t="b">
         <v>1</v>
       </c>
       <c r="D30" t="s">
@@ -1883,7 +1870,7 @@
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B31" t="s">
         <v>119</v>
@@ -1900,24 +1887,24 @@
     </row>
     <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B32" t="s">
         <v>139</v>
       </c>
-      <c r="C32" s="19" t="s">
+      <c r="C32" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="D32" s="19" t="s">
+      <c r="D32" s="18" t="s">
         <v>87</v>
       </c>
       <c r="E32" t="s">
-        <v>225</v>
+        <v>221</v>
       </c>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B33" t="s">
         <v>154</v>
@@ -1931,140 +1918,140 @@
     </row>
     <row r="34" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B34" t="s">
-        <v>178</v>
+        <v>174</v>
       </c>
       <c r="D34" t="s">
         <v>121</v>
       </c>
       <c r="E34" t="s">
-        <v>181</v>
+        <v>177</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B35" t="s">
-        <v>229</v>
+        <v>225</v>
       </c>
       <c r="D35" t="s">
         <v>121</v>
       </c>
       <c r="E35" t="s">
-        <v>180</v>
+        <v>176</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B36" t="s">
-        <v>190</v>
+        <v>186</v>
       </c>
       <c r="C36" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="D36" t="s">
         <v>87</v>
       </c>
       <c r="E36" t="s">
-        <v>224</v>
+        <v>220</v>
       </c>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B37" t="s">
-        <v>200</v>
+        <v>196</v>
       </c>
       <c r="C37" t="s">
-        <v>201</v>
+        <v>197</v>
       </c>
       <c r="D37" t="s">
         <v>87</v>
       </c>
       <c r="E37" t="s">
-        <v>202</v>
+        <v>198</v>
       </c>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B38" t="s">
-        <v>203</v>
-      </c>
-      <c r="C38" s="21" t="b">
+        <v>199</v>
+      </c>
+      <c r="C38" s="20" t="b">
         <v>1</v>
       </c>
       <c r="D38" t="s">
         <v>85</v>
       </c>
       <c r="E38" t="s">
-        <v>204</v>
+        <v>200</v>
       </c>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B39" t="s">
-        <v>215</v>
-      </c>
-      <c r="C39" s="21" t="b">
+        <v>211</v>
+      </c>
+      <c r="C39" s="20" t="b">
         <v>1</v>
       </c>
       <c r="D39" t="s">
         <v>85</v>
       </c>
       <c r="E39" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B40" t="s">
-        <v>217</v>
+        <v>213</v>
       </c>
       <c r="C40" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="D40" t="s">
         <v>87</v>
       </c>
       <c r="E40" t="s">
-        <v>223</v>
+        <v>219</v>
       </c>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B41" t="s">
-        <v>219</v>
+        <v>215</v>
       </c>
       <c r="C41" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="D41" t="s">
         <v>121</v>
       </c>
       <c r="E41" t="s">
-        <v>220</v>
+        <v>216</v>
       </c>
     </row>
     <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
-        <v>189</v>
+        <v>185</v>
       </c>
       <c r="B42" t="s">
-        <v>221</v>
+        <v>217</v>
       </c>
       <c r="C42">
         <v>2</v>
@@ -2073,7 +2060,7 @@
         <v>86</v>
       </c>
       <c r="E42" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
     </row>
   </sheetData>
@@ -2216,41 +2203,41 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
     </row>
-    <row r="3" spans="1:12" s="14" customFormat="1" ht="60" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="B3" s="13" t="s">
+    <row r="3" spans="1:12" s="13" customFormat="1" ht="60" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>169</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="C3" s="13" t="s">
+      <c r="C3" s="12" t="s">
         <v>150</v>
       </c>
-      <c r="D3" s="13" t="s">
+      <c r="D3" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="E3" s="13" t="s">
+      <c r="E3" s="12" t="s">
         <v>151</v>
       </c>
-      <c r="F3" s="13" t="s">
+      <c r="F3" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="G3" s="13" t="s">
+      <c r="G3" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H3" s="13" t="s">
+      <c r="H3" s="12" t="s">
         <v>152</v>
       </c>
-      <c r="I3" s="13" t="s">
+      <c r="I3" s="12" t="s">
         <v>19</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="K3" s="13" t="s">
+      <c r="K3" s="12" t="s">
         <v>18</v>
       </c>
-      <c r="L3" s="13" t="s">
+      <c r="L3" s="12" t="s">
         <v>21</v>
       </c>
     </row>
@@ -2410,7 +2397,7 @@
         <v>35</v>
       </c>
       <c r="H8" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J8">
         <v>0.752</v>
@@ -2446,7 +2433,7 @@
         <v>35</v>
       </c>
       <c r="H9" t="s">
-        <v>179</v>
+        <v>175</v>
       </c>
       <c r="J9">
         <v>0.65600000000000003</v>
@@ -2583,26 +2570,20 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B692AEE8-68EE-4B81-A49D-50BF066DFFE7}">
-  <dimension ref="A1:N91"/>
+  <dimension ref="A1:H91"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="20.5703125" customWidth="1"/>
-    <col min="2" max="2" width="22" customWidth="1"/>
-    <col min="3" max="3" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="15.7109375" customWidth="1"/>
-    <col min="6" max="6" width="22.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
-    <col min="9" max="9" width="20.42578125" customWidth="1"/>
-    <col min="10" max="10" width="9.42578125" customWidth="1"/>
-    <col min="11" max="11" width="15.85546875" customWidth="1"/>
-    <col min="12" max="12" width="12.85546875" customWidth="1"/>
-    <col min="13" max="13" width="15.7109375" customWidth="1"/>
-    <col min="14" max="14" width="42" customWidth="1"/>
+    <col min="2" max="2" width="24" customWidth="1"/>
+    <col min="3" max="3" width="20.42578125" customWidth="1"/>
+    <col min="4" max="4" width="9.42578125" customWidth="1"/>
+    <col min="5" max="5" width="15.85546875" customWidth="1"/>
+    <col min="6" max="6" width="12.85546875" customWidth="1"/>
+    <col min="7" max="7" width="15.7109375" customWidth="1"/>
+    <col min="8" max="8" width="42" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>4</v>
       </c>
@@ -2613,852 +2594,585 @@
         <v>5</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="E1" s="2" t="s">
         <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="H1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="J1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" s="2" t="s">
-        <v>5</v>
-      </c>
-      <c r="L1" s="2" t="s">
-        <v>6</v>
-      </c>
-      <c r="M1" s="2" t="s">
-        <v>7</v>
-      </c>
-      <c r="N1" s="2" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="2" spans="1:14" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>8</v>
       </c>
       <c r="B2" s="2"/>
       <c r="C2" s="2"/>
       <c r="D2" s="2"/>
-      <c r="E2" s="2"/>
+      <c r="E2" s="2" t="s">
+        <v>22</v>
+      </c>
       <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
+      <c r="G2" s="2" t="s">
+        <v>165</v>
+      </c>
       <c r="H2" s="2"/>
-      <c r="I2" s="2"/>
-      <c r="J2" s="2"/>
-      <c r="K2" s="2" t="s">
-        <v>22</v>
-      </c>
-      <c r="L2" s="2"/>
-      <c r="M2" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="N2" s="2"/>
-    </row>
-    <row r="3" spans="1:14" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
-        <v>174</v>
-      </c>
-      <c r="B3" s="6" t="s">
+    </row>
+    <row r="3" spans="1:8" ht="59.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
+        <v>170</v>
+      </c>
+      <c r="B3" s="5" t="s">
         <v>157</v>
       </c>
-      <c r="C3" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="D3" s="6" t="s">
+      <c r="C3" s="5" t="s">
         <v>158</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>151</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="I3" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="J3" s="6" t="s">
+      <c r="D3" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="K3" s="6" t="s">
+      <c r="E3" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="L3" s="6" t="s">
+      <c r="F3" s="5" t="s">
         <v>23</v>
       </c>
-      <c r="M3" s="8" t="s">
-        <v>168</v>
-      </c>
-      <c r="N3" s="9" t="s">
+      <c r="G3" s="7" t="s">
+        <v>164</v>
+      </c>
+      <c r="H3" s="8" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>40</v>
       </c>
-      <c r="B4" t="s">
-        <v>25</v>
-      </c>
-      <c r="C4" t="str">
-        <f>+_xlfn.XLOOKUP(H4,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>Source</v>
-      </c>
-      <c r="D4" t="s">
-        <v>24</v>
+      <c r="B4" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="C4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D4">
+        <v>60</v>
       </c>
       <c r="E4" t="s">
-        <v>27</v>
-      </c>
-      <c r="F4" t="str">
-        <f>+_xlfn.XLOOKUP(I4,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>First</v>
-      </c>
-      <c r="G4" t="s">
-        <v>24</v>
-      </c>
-      <c r="H4" s="3" t="str">
-        <f t="shared" ref="H4:H13" si="0">_xlfn.CONCAT(B4,":",D4)</f>
-        <v>Industrial_roundwood:FI</v>
-      </c>
-      <c r="I4" s="3" t="str">
-        <f t="shared" ref="I4:I13" si="1">_xlfn.CONCAT(E4,":",G4)</f>
-        <v>Sawmilling:FI</v>
-      </c>
-      <c r="J4">
-        <v>60</v>
-      </c>
-      <c r="K4" t="s">
         <v>39</v>
       </c>
-      <c r="L4">
+      <c r="F4">
         <v>2021</v>
       </c>
-      <c r="N4" s="10"/>
-    </row>
-    <row r="5" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H4" s="9"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>41</v>
       </c>
-      <c r="B5" t="s">
-        <v>27</v>
-      </c>
-      <c r="C5" t="str">
-        <f>+_xlfn.XLOOKUP(H5,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>First</v>
-      </c>
-      <c r="D5" t="s">
-        <v>24</v>
+      <c r="B5" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D5">
+        <v>100</v>
       </c>
       <c r="E5" t="s">
-        <v>26</v>
-      </c>
-      <c r="F5" t="str">
-        <f>+_xlfn.XLOOKUP(I5,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>Second</v>
-      </c>
-      <c r="G5" t="s">
-        <v>24</v>
-      </c>
-      <c r="H5" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Sawmilling:FI</v>
-      </c>
-      <c r="I5" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Sawnwood:FI</v>
-      </c>
-      <c r="J5">
-        <v>100</v>
-      </c>
-      <c r="K5" t="s">
         <v>9</v>
       </c>
-      <c r="L5">
+      <c r="F5">
         <v>2021</v>
       </c>
-      <c r="N5" s="10"/>
-    </row>
-    <row r="6" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H5" s="9"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>42</v>
       </c>
-      <c r="B6" t="s">
-        <v>27</v>
-      </c>
-      <c r="C6" t="str">
-        <f>+_xlfn.XLOOKUP(H6,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>First</v>
-      </c>
-      <c r="D6" t="s">
-        <v>24</v>
+      <c r="B6" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="D6">
+        <v>10</v>
       </c>
       <c r="E6" t="s">
-        <v>30</v>
-      </c>
-      <c r="F6" t="str">
-        <f>+_xlfn.XLOOKUP(I6,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>by_prod</v>
-      </c>
-      <c r="G6" t="s">
-        <v>24</v>
-      </c>
-      <c r="H6" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Sawmilling:FI</v>
-      </c>
-      <c r="I6" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Residues:FI</v>
-      </c>
-      <c r="J6">
-        <v>10</v>
-      </c>
-      <c r="K6" t="s">
         <v>39</v>
       </c>
-      <c r="L6">
+      <c r="F6">
         <v>2021</v>
       </c>
-      <c r="N6" s="10"/>
-    </row>
-    <row r="7" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H6" s="9"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>47</v>
       </c>
-      <c r="B7" t="s">
-        <v>26</v>
-      </c>
-      <c r="C7" t="str">
-        <f>+_xlfn.XLOOKUP(H7,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>Second</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
+      <c r="B7" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="D7">
+        <v>60</v>
       </c>
       <c r="E7" t="s">
-        <v>28</v>
-      </c>
-      <c r="F7" t="str">
-        <f>+_xlfn.XLOOKUP(I7,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>VAM</v>
-      </c>
-      <c r="G7" t="s">
-        <v>24</v>
-      </c>
-      <c r="H7" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Sawnwood:FI</v>
-      </c>
-      <c r="I7" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Construction:FI</v>
-      </c>
-      <c r="J7">
-        <v>60</v>
-      </c>
-      <c r="K7" t="s">
         <v>9</v>
       </c>
-      <c r="L7">
+      <c r="F7">
         <v>2021</v>
       </c>
-      <c r="M7">
+      <c r="G7">
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:14" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:8" ht="18.95" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>43</v>
       </c>
-      <c r="B8" t="s">
-        <v>26</v>
-      </c>
-      <c r="C8" t="str">
-        <f>+_xlfn.XLOOKUP(H8,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>Second</v>
-      </c>
-      <c r="D8" t="s">
-        <v>24</v>
+      <c r="B8" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C8" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="D8">
+        <v>40</v>
       </c>
       <c r="E8" t="s">
-        <v>29</v>
-      </c>
-      <c r="F8" t="str">
-        <f>+_xlfn.XLOOKUP(I8,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>VAM</v>
-      </c>
-      <c r="G8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H8" s="3" t="str">
-        <f>_xlfn.CONCAT(B8,":",D8)</f>
-        <v>Sawnwood:FI</v>
-      </c>
-      <c r="I8" s="3" t="str">
-        <f>_xlfn.CONCAT(E8,":",G8)</f>
-        <v>Furniture:FI</v>
-      </c>
-      <c r="J8">
-        <v>40</v>
-      </c>
-      <c r="K8" t="s">
         <v>9</v>
       </c>
-      <c r="L8">
+      <c r="F8">
         <v>2021</v>
       </c>
-      <c r="M8">
+      <c r="G8">
         <v>0.22500000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>44</v>
       </c>
-      <c r="B9" t="s">
-        <v>28</v>
-      </c>
-      <c r="C9" t="str">
-        <f>+_xlfn.XLOOKUP(H9,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>VAM</v>
-      </c>
-      <c r="D9" t="s">
-        <v>24</v>
+      <c r="B9" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D9">
+        <v>40</v>
       </c>
       <c r="E9" t="s">
-        <v>27</v>
-      </c>
-      <c r="F9" t="str">
-        <f>+_xlfn.XLOOKUP(I9,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>First</v>
-      </c>
-      <c r="G9" t="s">
-        <v>24</v>
-      </c>
-      <c r="H9" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Construction:FI</v>
-      </c>
-      <c r="I9" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Sawmilling:FI</v>
-      </c>
-      <c r="J9">
-        <v>40</v>
-      </c>
-      <c r="K9" t="s">
         <v>9</v>
       </c>
-      <c r="L9">
+      <c r="F9">
         <v>2021</v>
       </c>
     </row>
-    <row r="10" spans="1:14" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:8" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>45</v>
       </c>
-      <c r="B10" t="s">
-        <v>28</v>
-      </c>
-      <c r="C10" t="str">
-        <f>+_xlfn.XLOOKUP(H10,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>VAM</v>
-      </c>
-      <c r="D10" t="s">
-        <v>24</v>
+      <c r="B10" s="3" t="s">
+        <v>190</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D10">
+        <v>60</v>
       </c>
       <c r="E10" t="s">
-        <v>31</v>
-      </c>
-      <c r="F10" t="str">
-        <f>+_xlfn.XLOOKUP(I10,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>EoL</v>
-      </c>
-      <c r="G10" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Construction:FI</v>
-      </c>
-      <c r="I10" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Incineration:FI</v>
-      </c>
-      <c r="J10">
-        <v>60</v>
-      </c>
-      <c r="K10" t="s">
         <v>9</v>
       </c>
-      <c r="L10">
+      <c r="F10">
         <v>2021</v>
       </c>
     </row>
-    <row r="11" spans="1:14" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>46</v>
       </c>
-      <c r="B11" t="s">
-        <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>34</v>
-      </c>
-      <c r="D11" t="s">
-        <v>24</v>
+      <c r="B11" s="3" t="s">
+        <v>191</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D11">
+        <v>100</v>
       </c>
       <c r="E11" t="s">
-        <v>31</v>
-      </c>
-      <c r="F11" t="str">
-        <f>+_xlfn.XLOOKUP(I11,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>EoL</v>
-      </c>
-      <c r="G11" t="s">
-        <v>24</v>
-      </c>
-      <c r="H11" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Furniture:FI</v>
-      </c>
-      <c r="I11" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Incineration:FI</v>
-      </c>
-      <c r="J11">
-        <v>100</v>
-      </c>
-      <c r="K11" t="s">
         <v>9</v>
       </c>
-      <c r="L11">
+      <c r="F11">
         <v>2021</v>
       </c>
-      <c r="N11" s="10"/>
-    </row>
-    <row r="12" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H11" s="9"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>48</v>
       </c>
-      <c r="B12" t="s">
-        <v>26</v>
-      </c>
-      <c r="C12" t="str">
-        <f>+_xlfn.XLOOKUP(H12,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>Second</v>
-      </c>
-      <c r="D12" t="s">
-        <v>24</v>
+      <c r="B12" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D12">
+        <v>20</v>
       </c>
       <c r="E12" t="s">
-        <v>26</v>
-      </c>
-      <c r="F12" t="str">
-        <f>+_xlfn.XLOOKUP(I12,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>RoW</v>
-      </c>
-      <c r="G12" t="s">
-        <v>16</v>
-      </c>
-      <c r="H12" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Sawnwood:FI</v>
-      </c>
-      <c r="I12" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Sawnwood:Export</v>
-      </c>
-      <c r="J12">
-        <v>20</v>
-      </c>
-      <c r="K12" t="s">
         <v>39</v>
       </c>
-      <c r="L12">
+      <c r="F12">
         <v>2021</v>
       </c>
-      <c r="N12" s="10"/>
-    </row>
-    <row r="13" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="H12" s="9"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>49</v>
       </c>
-      <c r="B13" t="s">
-        <v>26</v>
-      </c>
-      <c r="C13" t="str">
-        <f>+_xlfn.XLOOKUP(H13,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>RoW</v>
-      </c>
-      <c r="D13" t="s">
-        <v>15</v>
+      <c r="B13" s="3" t="s">
+        <v>194</v>
+      </c>
+      <c r="C13" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="D13">
+        <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>26</v>
-      </c>
-      <c r="F13" t="str">
-        <f>+_xlfn.XLOOKUP(I13,Processes!$D$4:$D$47,Processes!$E$4:$E$47)</f>
-        <v>Second</v>
-      </c>
-      <c r="G13" t="s">
-        <v>24</v>
-      </c>
-      <c r="H13" s="3" t="str">
-        <f t="shared" si="0"/>
-        <v>Sawnwood:Import</v>
-      </c>
-      <c r="I13" s="3" t="str">
-        <f t="shared" si="1"/>
-        <v>Sawnwood:FI</v>
-      </c>
-      <c r="J13">
-        <v>10</v>
-      </c>
-      <c r="K13" t="s">
         <v>39</v>
       </c>
-      <c r="L13">
+      <c r="F13">
         <v>2021</v>
       </c>
-      <c r="N13" s="10"/>
-    </row>
-    <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H14" s="3"/>
-      <c r="I14" s="3"/>
-    </row>
-    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H15" s="3"/>
-      <c r="I15" s="3"/>
-    </row>
-    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="H16" s="3"/>
-      <c r="I16" s="3"/>
-    </row>
-    <row r="17" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H17" s="3"/>
-      <c r="I17" s="3"/>
-    </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H18" s="3"/>
-      <c r="I18" s="3"/>
-    </row>
-    <row r="19" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H19" s="3"/>
-      <c r="I19" s="3"/>
-    </row>
-    <row r="20" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H20" s="3"/>
-      <c r="I20" s="3"/>
-    </row>
-    <row r="21" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H21" s="3"/>
-      <c r="I21" s="3"/>
-    </row>
-    <row r="22" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H22" s="3"/>
-      <c r="I22" s="3"/>
-    </row>
-    <row r="23" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H23" s="3"/>
-      <c r="I23" s="3"/>
-    </row>
-    <row r="24" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H24" s="3"/>
-      <c r="I24" s="3"/>
-    </row>
-    <row r="25" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H25" s="3"/>
-      <c r="I25" s="3"/>
-    </row>
-    <row r="26" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H26" s="3"/>
-      <c r="I26" s="3"/>
-    </row>
-    <row r="27" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H27" s="3"/>
-      <c r="I27" s="3"/>
-    </row>
-    <row r="28" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H28" s="3"/>
-      <c r="I28" s="3"/>
-    </row>
-    <row r="29" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H29" s="3"/>
-      <c r="I29" s="3"/>
-    </row>
-    <row r="30" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H30" s="3"/>
-      <c r="I30" s="3"/>
-    </row>
-    <row r="31" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H31" s="3"/>
-      <c r="I31" s="3"/>
-    </row>
-    <row r="32" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H32" s="3"/>
-      <c r="I32" s="3"/>
-    </row>
-    <row r="33" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H33" s="3"/>
-      <c r="I33" s="3"/>
-    </row>
-    <row r="34" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H34" s="3"/>
-      <c r="I34" s="3"/>
-    </row>
-    <row r="35" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="E35" s="10"/>
-      <c r="H35" s="3"/>
-      <c r="I35" s="3"/>
-    </row>
-    <row r="36" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H36" s="3"/>
-      <c r="I36" s="3"/>
-    </row>
-    <row r="37" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H37" s="3"/>
-      <c r="I37" s="3"/>
-    </row>
-    <row r="38" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H38" s="3"/>
-      <c r="I38" s="3"/>
-    </row>
-    <row r="39" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H39" s="3"/>
-      <c r="I39" s="3"/>
-    </row>
-    <row r="40" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H40" s="3"/>
-      <c r="I40" s="3"/>
-    </row>
-    <row r="41" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H41" s="3"/>
-      <c r="I41" s="3"/>
-    </row>
-    <row r="42" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H42" s="3"/>
-      <c r="I42" s="3"/>
-    </row>
-    <row r="43" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H43" s="3"/>
-      <c r="I43" s="3"/>
-    </row>
-    <row r="44" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H44" s="3"/>
-      <c r="I44" s="3"/>
-    </row>
-    <row r="45" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C45" s="5"/>
-      <c r="H45" s="3"/>
-      <c r="I45" s="3"/>
-    </row>
-    <row r="46" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H46" s="3"/>
-      <c r="I46" s="3"/>
-    </row>
-    <row r="47" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H47" s="3"/>
-      <c r="I47" s="3"/>
-    </row>
-    <row r="48" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
-    </row>
-    <row r="49" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H49" s="3"/>
-      <c r="I49" s="3"/>
-    </row>
-    <row r="50" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H50" s="3"/>
-      <c r="I50" s="3"/>
-    </row>
-    <row r="51" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H51" s="3"/>
-      <c r="I51" s="3"/>
-    </row>
-    <row r="52" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H52" s="3"/>
-      <c r="I52" s="3"/>
-    </row>
-    <row r="53" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H53" s="3"/>
-      <c r="I53" s="3"/>
-    </row>
-    <row r="54" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H54" s="3"/>
-      <c r="I54" s="3"/>
-    </row>
-    <row r="55" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H55" s="3"/>
-      <c r="I55" s="3"/>
-    </row>
-    <row r="56" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H56" s="3"/>
-      <c r="I56" s="3"/>
-    </row>
-    <row r="57" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H57" s="3"/>
-      <c r="I57" s="3"/>
-    </row>
-    <row r="58" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H58" s="3"/>
-      <c r="I58" s="3"/>
-    </row>
-    <row r="59" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H59" s="3"/>
-      <c r="I59" s="3"/>
-    </row>
-    <row r="60" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H60" s="3"/>
-      <c r="I60" s="3"/>
-    </row>
-    <row r="61" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H61" s="3"/>
-      <c r="I61" s="3"/>
-    </row>
-    <row r="62" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H62" s="3"/>
-      <c r="I62" s="3"/>
-    </row>
-    <row r="63" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H63" s="3"/>
-      <c r="I63" s="3"/>
-    </row>
-    <row r="64" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H64" s="3"/>
-      <c r="I64" s="3"/>
-    </row>
-    <row r="65" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H65" s="3"/>
-      <c r="I65" s="3"/>
-    </row>
-    <row r="66" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H66" s="3"/>
-      <c r="I66" s="3"/>
-    </row>
-    <row r="67" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H67" s="3"/>
-      <c r="I67" s="3"/>
-    </row>
-    <row r="68" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H68" s="3"/>
-      <c r="I68" s="3"/>
-    </row>
-    <row r="69" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H69" s="3"/>
-      <c r="I69" s="3"/>
-    </row>
-    <row r="70" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H70" s="3"/>
-      <c r="I70" s="3"/>
-    </row>
-    <row r="71" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H71" s="3"/>
-      <c r="I71" s="3"/>
-    </row>
-    <row r="72" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H72" s="3"/>
-      <c r="I72" s="3"/>
-    </row>
-    <row r="73" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H73" s="3"/>
-      <c r="I73" s="3"/>
-    </row>
-    <row r="74" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H74" s="3"/>
-      <c r="I74" s="3"/>
-    </row>
-    <row r="75" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H75" s="3"/>
-      <c r="I75" s="3"/>
-    </row>
-    <row r="76" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H76" s="3"/>
-      <c r="I76" s="3"/>
-    </row>
-    <row r="77" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H77" s="3"/>
-      <c r="I77" s="3"/>
-    </row>
-    <row r="78" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H78" s="3"/>
-      <c r="I78" s="3"/>
-    </row>
-    <row r="79" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H79" s="3"/>
-      <c r="I79" s="3"/>
-    </row>
-    <row r="80" spans="8:9" x14ac:dyDescent="0.25">
-      <c r="H80" s="3"/>
-      <c r="I80" s="3"/>
-    </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="H81" s="3"/>
-      <c r="I81" s="3"/>
-    </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="H82" s="3"/>
-      <c r="I82" s="3"/>
-    </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="H83" s="3"/>
-      <c r="I83" s="3"/>
-    </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="H84" s="3"/>
-      <c r="I84" s="3"/>
-    </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="H85" s="3"/>
-      <c r="I85" s="3"/>
-    </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.25">
+      <c r="H13" s="9"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B14" s="3"/>
+      <c r="C14" s="3"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B15" s="3"/>
+      <c r="C15" s="3"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="B16" s="3"/>
+      <c r="C16" s="3"/>
+    </row>
+    <row r="17" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B17" s="3"/>
+      <c r="C17" s="3"/>
+    </row>
+    <row r="18" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B18" s="3"/>
+      <c r="C18" s="3"/>
+    </row>
+    <row r="19" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B19" s="3"/>
+      <c r="C19" s="3"/>
+    </row>
+    <row r="20" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B20" s="3"/>
+      <c r="C20" s="3"/>
+    </row>
+    <row r="21" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B21" s="3"/>
+      <c r="C21" s="3"/>
+    </row>
+    <row r="22" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B22" s="3"/>
+      <c r="C22" s="3"/>
+    </row>
+    <row r="23" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B23" s="3"/>
+      <c r="C23" s="3"/>
+    </row>
+    <row r="24" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B24" s="3"/>
+      <c r="C24" s="3"/>
+    </row>
+    <row r="25" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B25" s="3"/>
+      <c r="C25" s="3"/>
+    </row>
+    <row r="26" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B26" s="3"/>
+      <c r="C26" s="3"/>
+    </row>
+    <row r="27" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B27" s="3"/>
+      <c r="C27" s="3"/>
+    </row>
+    <row r="28" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B28" s="3"/>
+      <c r="C28" s="3"/>
+    </row>
+    <row r="29" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B29" s="3"/>
+      <c r="C29" s="3"/>
+    </row>
+    <row r="30" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B30" s="3"/>
+      <c r="C30" s="3"/>
+    </row>
+    <row r="31" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B31" s="3"/>
+      <c r="C31" s="3"/>
+    </row>
+    <row r="32" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B32" s="3"/>
+      <c r="C32" s="3"/>
+    </row>
+    <row r="33" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B33" s="3"/>
+      <c r="C33" s="3"/>
+    </row>
+    <row r="34" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B34" s="3"/>
+      <c r="C34" s="3"/>
+    </row>
+    <row r="35" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B35" s="3"/>
+      <c r="C35" s="3"/>
+    </row>
+    <row r="36" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B36" s="3"/>
+      <c r="C36" s="3"/>
+    </row>
+    <row r="37" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B37" s="3"/>
+      <c r="C37" s="3"/>
+    </row>
+    <row r="38" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B38" s="3"/>
+      <c r="C38" s="3"/>
+    </row>
+    <row r="39" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B39" s="3"/>
+      <c r="C39" s="3"/>
+    </row>
+    <row r="40" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B40" s="3"/>
+      <c r="C40" s="3"/>
+    </row>
+    <row r="41" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B41" s="3"/>
+      <c r="C41" s="3"/>
+    </row>
+    <row r="42" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B42" s="3"/>
+      <c r="C42" s="3"/>
+    </row>
+    <row r="43" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B43" s="3"/>
+      <c r="C43" s="3"/>
+    </row>
+    <row r="44" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B44" s="3"/>
+      <c r="C44" s="3"/>
+    </row>
+    <row r="45" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+    </row>
+    <row r="46" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B46" s="3"/>
+      <c r="C46" s="3"/>
+    </row>
+    <row r="47" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
+    </row>
+    <row r="48" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B48" s="3"/>
+      <c r="C48" s="3"/>
+    </row>
+    <row r="49" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+    </row>
+    <row r="50" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B50" s="3"/>
+      <c r="C50" s="3"/>
+    </row>
+    <row r="51" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+    </row>
+    <row r="52" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B52" s="3"/>
+      <c r="C52" s="3"/>
+    </row>
+    <row r="53" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+    </row>
+    <row r="54" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B54" s="3"/>
+      <c r="C54" s="3"/>
+    </row>
+    <row r="55" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+    </row>
+    <row r="56" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B56" s="3"/>
+      <c r="C56" s="3"/>
+    </row>
+    <row r="57" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+    </row>
+    <row r="58" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B58" s="3"/>
+      <c r="C58" s="3"/>
+    </row>
+    <row r="59" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B59" s="3"/>
+      <c r="C59" s="3"/>
+    </row>
+    <row r="60" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B60" s="3"/>
+      <c r="C60" s="3"/>
+    </row>
+    <row r="61" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B61" s="3"/>
+      <c r="C61" s="3"/>
+    </row>
+    <row r="62" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B62" s="3"/>
+      <c r="C62" s="3"/>
+    </row>
+    <row r="63" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B63" s="3"/>
+      <c r="C63" s="3"/>
+    </row>
+    <row r="64" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B64" s="3"/>
+      <c r="C64" s="3"/>
+    </row>
+    <row r="65" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B65" s="3"/>
+      <c r="C65" s="3"/>
+    </row>
+    <row r="66" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B66" s="3"/>
+      <c r="C66" s="3"/>
+    </row>
+    <row r="67" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B67" s="3"/>
+      <c r="C67" s="3"/>
+    </row>
+    <row r="68" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B68" s="3"/>
+      <c r="C68" s="3"/>
+    </row>
+    <row r="69" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B69" s="3"/>
+      <c r="C69" s="3"/>
+    </row>
+    <row r="70" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B70" s="3"/>
+      <c r="C70" s="3"/>
+    </row>
+    <row r="71" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B71" s="3"/>
+      <c r="C71" s="3"/>
+    </row>
+    <row r="72" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B72" s="3"/>
+      <c r="C72" s="3"/>
+    </row>
+    <row r="73" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B73" s="3"/>
+      <c r="C73" s="3"/>
+    </row>
+    <row r="74" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B74" s="3"/>
+      <c r="C74" s="3"/>
+    </row>
+    <row r="75" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B75" s="3"/>
+      <c r="C75" s="3"/>
+    </row>
+    <row r="76" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+    </row>
+    <row r="77" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+    </row>
+    <row r="78" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B78" s="3"/>
+      <c r="C78" s="3"/>
+    </row>
+    <row r="79" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B79" s="3"/>
+      <c r="C79" s="3"/>
+    </row>
+    <row r="80" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+    </row>
+    <row r="81" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+    </row>
+    <row r="82" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B82" s="3"/>
+      <c r="C82" s="3"/>
+    </row>
+    <row r="83" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B83" s="3"/>
+      <c r="C83" s="3"/>
+    </row>
+    <row r="84" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+    </row>
+    <row r="85" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+    </row>
+    <row r="87" spans="2:3" x14ac:dyDescent="0.25">
       <c r="B87" s="3"/>
-      <c r="D87" s="3"/>
-      <c r="E87" s="3"/>
-      <c r="G87" s="3"/>
-      <c r="H87" s="3"/>
-      <c r="I87" s="3"/>
-    </row>
-    <row r="88" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="H88" s="3"/>
-      <c r="I88" s="3"/>
-    </row>
-    <row r="89" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="H89" s="3"/>
-      <c r="I89" s="3"/>
-    </row>
-    <row r="90" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="H90" s="3"/>
-      <c r="I90" s="3"/>
-    </row>
-    <row r="91" spans="2:9" x14ac:dyDescent="0.25">
-      <c r="H91" s="3"/>
-      <c r="I91" s="3"/>
+      <c r="C87" s="3"/>
+    </row>
+    <row r="88" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B88" s="3"/>
+      <c r="C88" s="3"/>
+    </row>
+    <row r="89" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B89" s="3"/>
+      <c r="C89" s="3"/>
+    </row>
+    <row r="90" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B90" s="3"/>
+      <c r="C90" s="3"/>
+    </row>
+    <row r="91" spans="2:3" x14ac:dyDescent="0.25">
+      <c r="B91" s="3"/>
+      <c r="C91" s="3"/>
     </row>
   </sheetData>
-  <autoFilter ref="A3:N13" xr:uid="{B692AEE8-68EE-4B81-A49D-50BF066DFFE7}"/>
+  <autoFilter ref="A3:H13" xr:uid="{B692AEE8-68EE-4B81-A49D-50BF066DFFE7}"/>
   <phoneticPr fontId="4" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3498,13 +3212,13 @@
         <v>5</v>
       </c>
       <c r="F1" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="G1" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="H1" s="2" t="s">
-        <v>205</v>
+        <v>201</v>
       </c>
       <c r="I1" s="2" t="s">
         <v>5</v>
@@ -3528,43 +3242,43 @@
       <c r="J2" s="2"/>
     </row>
     <row r="3" spans="1:10" ht="60.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="12" t="s">
+      <c r="A3" s="11" t="s">
+        <v>202</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C3" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>107</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>108</v>
+      </c>
+      <c r="F3" s="5" t="s">
+        <v>203</v>
+      </c>
+      <c r="G3" s="5" t="s">
+        <v>204</v>
+      </c>
+      <c r="H3" s="5" t="s">
+        <v>205</v>
+      </c>
+      <c r="I3" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="B3" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>56</v>
-      </c>
-      <c r="D3" s="6" t="s">
-        <v>107</v>
-      </c>
-      <c r="E3" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="F3" s="6" t="s">
-        <v>207</v>
-      </c>
-      <c r="G3" s="6" t="s">
-        <v>208</v>
-      </c>
-      <c r="H3" s="6" t="s">
-        <v>209</v>
-      </c>
-      <c r="I3" s="7" t="s">
-        <v>210</v>
-      </c>
-      <c r="J3" s="6" t="s">
+      <c r="J3" s="5" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="B4" t="s">
-        <v>232</v>
+        <v>228</v>
       </c>
       <c r="C4">
         <v>5</v>
@@ -3579,10 +3293,10 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="B5" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C5">
         <v>0</v>
@@ -3596,10 +3310,10 @@
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="B6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="D6">
         <v>2026</v>
@@ -3610,10 +3324,10 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="B7" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C7">
         <v>5</v>
@@ -3624,10 +3338,10 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="B8" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C8">
         <v>5</v>
@@ -3641,10 +3355,10 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="B9" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C9">
         <v>5</v>
@@ -3658,10 +3372,10 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>239</v>
+        <v>235</v>
       </c>
       <c r="B10" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C10">
         <v>5</v>
@@ -3672,10 +3386,10 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="B11" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C11">
         <v>5</v>
@@ -3689,10 +3403,10 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>240</v>
+        <v>236</v>
       </c>
       <c r="B12" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C12">
         <v>5</v>
@@ -3704,15 +3418,15 @@
         <v>1900</v>
       </c>
       <c r="F12" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="B13" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C13">
         <v>5</v>
@@ -3724,15 +3438,15 @@
         <v>1900</v>
       </c>
       <c r="G13" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="B14" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C14">
         <v>5</v>
@@ -3744,15 +3458,15 @@
         <v>1900</v>
       </c>
       <c r="H14" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>243</v>
+        <v>239</v>
       </c>
       <c r="B15" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C15">
         <v>5</v>
@@ -3764,7 +3478,7 @@
         <v>1900</v>
       </c>
       <c r="I15" t="s">
-        <v>230</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -3819,7 +3533,7 @@
         <v>2021</v>
       </c>
       <c r="B2" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C2">
         <v>3.6999999999999998E-2</v>
@@ -3847,7 +3561,7 @@
         <v>2021</v>
       </c>
       <c r="B4" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C4">
         <v>0.40899999999999997</v>
@@ -3875,7 +3589,7 @@
         <v>2021</v>
       </c>
       <c r="B6" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C6">
         <v>0.752</v>
@@ -3889,7 +3603,7 @@
         <v>2021</v>
       </c>
       <c r="B7" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C7">
         <v>0.65600000000000003</v>
@@ -3903,7 +3617,7 @@
         <v>2021</v>
       </c>
       <c r="B8" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C8">
         <v>0.96599999999999997</v>
@@ -3917,7 +3631,7 @@
         <v>2021</v>
       </c>
       <c r="B9" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C9">
         <v>0.69099999999999995</v>
@@ -3931,7 +3645,7 @@
         <v>2021</v>
       </c>
       <c r="B10" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C10">
         <v>0.24299999999999999</v>
@@ -3945,7 +3659,7 @@
         <v>2022</v>
       </c>
       <c r="B11" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C11">
         <v>3.6999999999999998E-2</v>
@@ -3973,7 +3687,7 @@
         <v>2022</v>
       </c>
       <c r="B13" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C13">
         <v>0.40899999999999997</v>
@@ -4001,7 +3715,7 @@
         <v>2022</v>
       </c>
       <c r="B15" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C15">
         <v>0.752</v>
@@ -4015,7 +3729,7 @@
         <v>2022</v>
       </c>
       <c r="B16" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C16">
         <v>0.65600000000000003</v>
@@ -4029,7 +3743,7 @@
         <v>2022</v>
       </c>
       <c r="B17" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C17">
         <v>0.96599999999999997</v>
@@ -4043,7 +3757,7 @@
         <v>2022</v>
       </c>
       <c r="B18" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C18">
         <v>0.69099999999999995</v>
@@ -4057,7 +3771,7 @@
         <v>2022</v>
       </c>
       <c r="B19" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C19">
         <v>0.24299999999999999</v>
@@ -4071,7 +3785,7 @@
         <v>2023</v>
       </c>
       <c r="B20" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C20">
         <v>3.6999999999999998E-2</v>
@@ -4099,7 +3813,7 @@
         <v>2023</v>
       </c>
       <c r="B22" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C22">
         <v>0.40899999999999997</v>
@@ -4127,7 +3841,7 @@
         <v>2023</v>
       </c>
       <c r="B24" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C24">
         <v>0.752</v>
@@ -4141,7 +3855,7 @@
         <v>2023</v>
       </c>
       <c r="B25" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C25">
         <v>0.65600000000000003</v>
@@ -4155,7 +3869,7 @@
         <v>2023</v>
       </c>
       <c r="B26" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C26">
         <v>0.96599999999999997</v>
@@ -4169,7 +3883,7 @@
         <v>2023</v>
       </c>
       <c r="B27" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C27">
         <v>0.69099999999999995</v>
@@ -4183,7 +3897,7 @@
         <v>2023</v>
       </c>
       <c r="B28" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C28">
         <v>0.24299999999999999</v>
@@ -4197,7 +3911,7 @@
         <v>2024</v>
       </c>
       <c r="B29" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C29">
         <v>3.6999999999999998E-2</v>
@@ -4225,7 +3939,7 @@
         <v>2024</v>
       </c>
       <c r="B31" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C31">
         <v>0.40899999999999997</v>
@@ -4253,7 +3967,7 @@
         <v>2024</v>
       </c>
       <c r="B33" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C33">
         <v>0.752</v>
@@ -4267,7 +3981,7 @@
         <v>2024</v>
       </c>
       <c r="B34" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C34">
         <v>0.65600000000000003</v>
@@ -4281,7 +3995,7 @@
         <v>2024</v>
       </c>
       <c r="B35" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C35">
         <v>0.96599999999999997</v>
@@ -4295,7 +4009,7 @@
         <v>2024</v>
       </c>
       <c r="B36" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C36">
         <v>0.69099999999999995</v>
@@ -4309,7 +4023,7 @@
         <v>2024</v>
       </c>
       <c r="B37" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C37">
         <v>0.24299999999999999</v>
@@ -4323,7 +4037,7 @@
         <v>2025</v>
       </c>
       <c r="B38" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C38">
         <v>3.6999999999999998E-2</v>
@@ -4351,7 +4065,7 @@
         <v>2025</v>
       </c>
       <c r="B40" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C40">
         <v>0.40899999999999997</v>
@@ -4379,7 +4093,7 @@
         <v>2025</v>
       </c>
       <c r="B42" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C42">
         <v>0.752</v>
@@ -4393,7 +4107,7 @@
         <v>2025</v>
       </c>
       <c r="B43" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C43">
         <v>0.65600000000000003</v>
@@ -4407,7 +4121,7 @@
         <v>2025</v>
       </c>
       <c r="B44" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C44">
         <v>0.96599999999999997</v>
@@ -4421,7 +4135,7 @@
         <v>2025</v>
       </c>
       <c r="B45" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C45">
         <v>0.69099999999999995</v>
@@ -4435,7 +4149,7 @@
         <v>2025</v>
       </c>
       <c r="B46" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C46">
         <v>0.24299999999999999</v>
@@ -4449,7 +4163,7 @@
         <v>2026</v>
       </c>
       <c r="B47" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C47">
         <v>3.6999999999999998E-2</v>
@@ -4477,7 +4191,7 @@
         <v>2026</v>
       </c>
       <c r="B49" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C49">
         <v>0.40899999999999997</v>
@@ -4505,7 +4219,7 @@
         <v>2026</v>
       </c>
       <c r="B51" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C51">
         <v>0.752</v>
@@ -4519,7 +4233,7 @@
         <v>2026</v>
       </c>
       <c r="B52" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C52">
         <v>0.65600000000000003</v>
@@ -4533,7 +4247,7 @@
         <v>2026</v>
       </c>
       <c r="B53" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C53">
         <v>0.96599999999999997</v>
@@ -4547,7 +4261,7 @@
         <v>2026</v>
       </c>
       <c r="B54" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C54">
         <v>0.69099999999999995</v>
@@ -4561,7 +4275,7 @@
         <v>2026</v>
       </c>
       <c r="B55" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C55">
         <v>0.24299999999999999</v>
@@ -4575,7 +4289,7 @@
         <v>2027</v>
       </c>
       <c r="B56" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C56">
         <v>3.6999999999999998E-2</v>
@@ -4603,7 +4317,7 @@
         <v>2027</v>
       </c>
       <c r="B58" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C58">
         <v>0.40899999999999997</v>
@@ -4631,7 +4345,7 @@
         <v>2027</v>
       </c>
       <c r="B60" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C60">
         <v>0.752</v>
@@ -4645,7 +4359,7 @@
         <v>2027</v>
       </c>
       <c r="B61" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C61">
         <v>0.65600000000000003</v>
@@ -4659,7 +4373,7 @@
         <v>2027</v>
       </c>
       <c r="B62" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C62">
         <v>0.96599999999999997</v>
@@ -4673,7 +4387,7 @@
         <v>2027</v>
       </c>
       <c r="B63" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C63">
         <v>0.69099999999999995</v>
@@ -4687,7 +4401,7 @@
         <v>2027</v>
       </c>
       <c r="B64" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C64">
         <v>0.24299999999999999</v>
@@ -4701,7 +4415,7 @@
         <v>2028</v>
       </c>
       <c r="B65" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C65">
         <v>3.6999999999999998E-2</v>
@@ -4729,7 +4443,7 @@
         <v>2028</v>
       </c>
       <c r="B67" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C67">
         <v>0.40899999999999997</v>
@@ -4757,7 +4471,7 @@
         <v>2028</v>
       </c>
       <c r="B69" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C69">
         <v>0.752</v>
@@ -4771,7 +4485,7 @@
         <v>2028</v>
       </c>
       <c r="B70" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C70">
         <v>0.65600000000000003</v>
@@ -4785,7 +4499,7 @@
         <v>2028</v>
       </c>
       <c r="B71" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C71">
         <v>0.96599999999999997</v>
@@ -4799,7 +4513,7 @@
         <v>2028</v>
       </c>
       <c r="B72" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C72">
         <v>0.69099999999999995</v>
@@ -4813,7 +4527,7 @@
         <v>2028</v>
       </c>
       <c r="B73" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C73">
         <v>0.24299999999999999</v>
@@ -4827,7 +4541,7 @@
         <v>2029</v>
       </c>
       <c r="B74" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C74">
         <v>3.6999999999999998E-2</v>
@@ -4855,7 +4569,7 @@
         <v>2029</v>
       </c>
       <c r="B76" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C76">
         <v>0.40899999999999997</v>
@@ -4883,7 +4597,7 @@
         <v>2029</v>
       </c>
       <c r="B78" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C78">
         <v>0.752</v>
@@ -4897,7 +4611,7 @@
         <v>2029</v>
       </c>
       <c r="B79" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C79">
         <v>0.65600000000000003</v>
@@ -4911,7 +4625,7 @@
         <v>2029</v>
       </c>
       <c r="B80" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C80">
         <v>0.96599999999999997</v>
@@ -4925,7 +4639,7 @@
         <v>2029</v>
       </c>
       <c r="B81" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C81">
         <v>0.69099999999999995</v>
@@ -4939,7 +4653,7 @@
         <v>2029</v>
       </c>
       <c r="B82" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C82">
         <v>0.24299999999999999</v>
@@ -4953,7 +4667,7 @@
         <v>2030</v>
       </c>
       <c r="B83" t="s">
-        <v>192</v>
+        <v>188</v>
       </c>
       <c r="C83">
         <v>3.6999999999999998E-2</v>
@@ -4981,7 +4695,7 @@
         <v>2030</v>
       </c>
       <c r="B85" t="s">
-        <v>193</v>
+        <v>189</v>
       </c>
       <c r="C85">
         <v>0.40899999999999997</v>
@@ -5009,7 +4723,7 @@
         <v>2030</v>
       </c>
       <c r="B87" t="s">
-        <v>194</v>
+        <v>190</v>
       </c>
       <c r="C87">
         <v>0.752</v>
@@ -5023,7 +4737,7 @@
         <v>2030</v>
       </c>
       <c r="B88" t="s">
-        <v>195</v>
+        <v>191</v>
       </c>
       <c r="C88">
         <v>0.65600000000000003</v>
@@ -5037,7 +4751,7 @@
         <v>2030</v>
       </c>
       <c r="B89" t="s">
-        <v>196</v>
+        <v>192</v>
       </c>
       <c r="C89">
         <v>0.96599999999999997</v>
@@ -5051,7 +4765,7 @@
         <v>2030</v>
       </c>
       <c r="B90" t="s">
-        <v>197</v>
+        <v>193</v>
       </c>
       <c r="C90">
         <v>0.69099999999999995</v>
@@ -5065,7 +4779,7 @@
         <v>2030</v>
       </c>
       <c r="B91" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="C91">
         <v>0.24299999999999999</v>
@@ -5098,46 +4812,46 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A1" s="22" t="s">
+      <c r="A1" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="B1" s="22" t="s">
+      <c r="B1" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="C1" s="22" t="s">
+      <c r="C1" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="E1" s="22" t="s">
-        <v>177</v>
-      </c>
-      <c r="F1" s="22" t="s">
+      <c r="E1" s="21" t="s">
+        <v>173</v>
+      </c>
+      <c r="F1" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="J1" s="22" t="s">
-        <v>199</v>
-      </c>
-      <c r="K1" s="22" t="s">
+      <c r="J1" s="21" t="s">
+        <v>195</v>
+      </c>
+      <c r="K1" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="L1" s="22" t="s">
+      <c r="L1" s="21" t="s">
         <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>36</v>
@@ -5160,7 +4874,7 @@
       <c r="I2" t="s">
         <v>116</v>
       </c>
-      <c r="J2" s="21" t="b">
+      <c r="J2" s="20" t="b">
         <v>1</v>
       </c>
     </row>
@@ -5320,26 +5034,26 @@
       </c>
     </row>
     <row r="5" spans="2:8" x14ac:dyDescent="0.25">
-      <c r="B5" s="15" t="s">
+      <c r="B5" s="14" t="s">
         <v>81</v>
       </c>
-      <c r="C5" s="15" t="s">
+      <c r="C5" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="D5" s="15" t="s">
+      <c r="D5" s="14" t="s">
         <v>90</v>
       </c>
-      <c r="E5" s="15" t="s">
+      <c r="E5" s="14" t="s">
         <v>114</v>
       </c>
-      <c r="F5" s="15" t="s">
+      <c r="F5" s="14" t="s">
         <v>109</v>
       </c>
-      <c r="G5" s="15" t="s">
-        <v>185</v>
-      </c>
-      <c r="H5" s="15" t="s">
-        <v>211</v>
+      <c r="G5" s="14" t="s">
+        <v>181</v>
+      </c>
+      <c r="H5" s="14" t="s">
+        <v>207</v>
       </c>
     </row>
     <row r="6" spans="2:8" x14ac:dyDescent="0.25">
@@ -5359,10 +5073,10 @@
         <v>115</v>
       </c>
       <c r="G6" t="s">
-        <v>186</v>
+        <v>182</v>
       </c>
       <c r="H6" t="s">
-        <v>212</v>
+        <v>208</v>
       </c>
     </row>
     <row r="7" spans="2:8" x14ac:dyDescent="0.25">
@@ -5382,10 +5096,10 @@
         <v>116</v>
       </c>
       <c r="G7" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="H7" t="s">
-        <v>213</v>
+        <v>209</v>
       </c>
     </row>
     <row r="8" spans="2:8" x14ac:dyDescent="0.25">
@@ -5399,7 +5113,7 @@
         <v>117</v>
       </c>
       <c r="H8" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
     </row>
     <row r="9" spans="2:8" x14ac:dyDescent="0.25">
@@ -5425,12 +5139,12 @@
     </row>
     <row r="12" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B12" t="s">
-        <v>182</v>
+        <v>178</v>
       </c>
     </row>
     <row r="13" spans="2:8" x14ac:dyDescent="0.25">
       <c r="B13" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>
@@ -5452,15 +5166,6 @@
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Asiakirja" ma:contentTypeID="0x010100806C55B750152A459818B636E97A41C3" ma:contentTypeVersion="19" ma:contentTypeDescription="Luo uusi asiakirja." ma:contentTypeScope="" ma:versionID="74fd9cb75cef04cf26a1ff9ddef01b4b">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="7536dd80-7d39-48e8-9ae3-b4166f580a2d" xmlns:ns3="145cc194-9bea-4db6-b116-a042a4529fcd" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="afbcbfdd38894bc2ff0644b00c8ec680" ns2:_="" ns3:_="">
     <xsd:import namespace="7536dd80-7d39-48e8-9ae3-b4166f580a2d"/>
@@ -5723,6 +5428,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{557FAA9C-B184-448F-B58D-00E4D46BDD72}">
   <ds:schemaRefs>
@@ -5741,14 +5455,6 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{D60021C7-CA75-4673-96EA-55284BF81134}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -5765,4 +5471,12 @@
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8AB3C6F0-DB35-46F0-8FEB-B5E57B48A727}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>